--- a/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="110">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -105,231 +105,216 @@
     <t>12 - 11</t>
   </si>
   <si>
+    <t>MACAM EMPREENDIMENTOS C I L ME</t>
+  </si>
+  <si>
     <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
   </si>
   <si>
-    <t>MACAM EMPREENDIMENTOS C I L ME</t>
-  </si>
-  <si>
     <t>02/12/2026</t>
   </si>
   <si>
     <t>Vivo</t>
   </si>
   <si>
-    <t>04/12/2026</t>
+    <t>05/12/2026</t>
+  </si>
+  <si>
+    <t>1 - 10</t>
+  </si>
+  <si>
+    <t>BIANCA RODRIGUES</t>
+  </si>
+  <si>
+    <t>1 - 9</t>
+  </si>
+  <si>
+    <t>FELIPE DOMINGOS BARBOSA</t>
+  </si>
+  <si>
+    <t>Hostgator</t>
+  </si>
+  <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>1 - 11</t>
+  </si>
+  <si>
+    <t>DECORA INTERIORES LTDA</t>
+  </si>
+  <si>
+    <t>3 - 10</t>
+  </si>
+  <si>
+    <t>Promob</t>
+  </si>
+  <si>
+    <t>Jackson Fernando de Araujo</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>FERNANDO OLIVEIRA LEITE</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>SINDICATO DO COM VAREJ E LOJISTA DO COM DE SP - SI</t>
+  </si>
+  <si>
+    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>Sabesp</t>
+  </si>
+  <si>
+    <t>Thais Pereira Pires</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>61 - 7</t>
+  </si>
+  <si>
+    <t>Pipefy</t>
+  </si>
+  <si>
+    <t>62 - 6</t>
+  </si>
+  <si>
+    <t>63 - 6</t>
+  </si>
+  <si>
+    <t>67 - 5</t>
+  </si>
+  <si>
+    <t>Mercado livre</t>
+  </si>
+  <si>
+    <t>70 - 3</t>
+  </si>
+  <si>
+    <t>71 - 3</t>
+  </si>
+  <si>
+    <t>72 - 3</t>
+  </si>
+  <si>
+    <t>73 - 3</t>
+  </si>
+  <si>
+    <t>MP  MARKFERRAGENS</t>
+  </si>
+  <si>
+    <t>08/12/2026</t>
+  </si>
+  <si>
+    <t>10/12/2026</t>
+  </si>
+  <si>
+    <t>Roger Duarte Pinheiro Me</t>
+  </si>
+  <si>
+    <t>PREFEITURA SP- ISS</t>
+  </si>
+  <si>
+    <t>12/12/2026</t>
+  </si>
+  <si>
+    <t>2 - 11</t>
+  </si>
+  <si>
+    <t>Enel</t>
+  </si>
+  <si>
+    <t>18/12/2026</t>
+  </si>
+  <si>
+    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
+  </si>
+  <si>
+    <t>12 - 10</t>
+  </si>
+  <si>
+    <t>VERISURE</t>
+  </si>
+  <si>
+    <t>PFR-Previsões Financeiras a Receber</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>20/12/2026</t>
+  </si>
+  <si>
+    <t>INSS- Previdenciária</t>
+  </si>
+  <si>
+    <t>IRRF- darf</t>
+  </si>
+  <si>
+    <t>Simples Nacional - DAS</t>
+  </si>
+  <si>
+    <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
+  </si>
+  <si>
+    <t>22/12/2026</t>
+  </si>
+  <si>
+    <t>64 - 6</t>
+  </si>
+  <si>
+    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
+  </si>
+  <si>
+    <t>25/12/2026</t>
+  </si>
+  <si>
+    <t>68 - 5</t>
+  </si>
+  <si>
+    <t>Luis Carlos Alves de Oliveira</t>
+  </si>
+  <si>
+    <t>26/12/2026</t>
+  </si>
+  <si>
+    <t>EM SOLUCOES INTEGRADAS DE SISTEMAS LTDA ME</t>
+  </si>
+  <si>
+    <t>30/12/2026</t>
   </si>
   <si>
     <t>DUP-Duplicata de Contrato</t>
   </si>
   <si>
-    <t>102301 - 2</t>
-  </si>
-  <si>
-    <t>Thiago Souza Dias Degola</t>
-  </si>
-  <si>
-    <t>05/12/2026</t>
-  </si>
-  <si>
-    <t>100901 - 2</t>
-  </si>
-  <si>
-    <t>Mariana Andrade Derossi</t>
-  </si>
-  <si>
-    <t>1 - 10</t>
-  </si>
-  <si>
-    <t>BIANCA RODRIGUES</t>
-  </si>
-  <si>
-    <t>1 - 9</t>
-  </si>
-  <si>
-    <t>FELIPE DOMINGOS BARBOSA</t>
-  </si>
-  <si>
-    <t>1 - 11</t>
-  </si>
-  <si>
-    <t>DECORA INTERIORES LTDA</t>
-  </si>
-  <si>
-    <t>Hostgator</t>
-  </si>
-  <si>
-    <t>FERNANDA DOCHVAT SILVA</t>
-  </si>
-  <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
-    <t>3 - 10</t>
-  </si>
-  <si>
-    <t>Promob</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>FERNANDO OLIVEIRA LEITE</t>
-  </si>
-  <si>
-    <t>Carina Pereira</t>
-  </si>
-  <si>
-    <t>SINDICATO DO COM VAREJ E LOJISTA DO COM DE SP - SI</t>
-  </si>
-  <si>
-    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>Jackson Fernando de Araujo</t>
-  </si>
-  <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>Sabesp</t>
-  </si>
-  <si>
-    <t>Thais Pereira Pires</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>61 - 7</t>
-  </si>
-  <si>
-    <t>Pipefy</t>
-  </si>
-  <si>
-    <t>62 - 6</t>
-  </si>
-  <si>
-    <t>63 - 6</t>
-  </si>
-  <si>
-    <t>67 - 5</t>
-  </si>
-  <si>
-    <t>Mercado livre</t>
-  </si>
-  <si>
-    <t>70 - 3</t>
-  </si>
-  <si>
-    <t>71 - 3</t>
-  </si>
-  <si>
-    <t>72 - 3</t>
-  </si>
-  <si>
-    <t>73 - 3</t>
-  </si>
-  <si>
-    <t>MP  MARKFERRAGENS</t>
-  </si>
-  <si>
-    <t>08/12/2026</t>
-  </si>
-  <si>
-    <t>10/12/2026</t>
-  </si>
-  <si>
-    <t>Roger Duarte Pinheiro Me</t>
-  </si>
-  <si>
-    <t>PREFEITURA SP- ISS</t>
-  </si>
-  <si>
-    <t>12/12/2026</t>
-  </si>
-  <si>
-    <t>2 - 11</t>
-  </si>
-  <si>
-    <t>Enel</t>
-  </si>
-  <si>
-    <t>18/12/2026</t>
-  </si>
-  <si>
-    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
-  </si>
-  <si>
-    <t>12 - 10</t>
-  </si>
-  <si>
-    <t>VERISURE</t>
-  </si>
-  <si>
-    <t>PFR-Previsões Financeiras a Receber</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>20/12/2026</t>
-  </si>
-  <si>
-    <t>INSS- Previdenciária</t>
-  </si>
-  <si>
-    <t>IRRF- darf</t>
-  </si>
-  <si>
-    <t>Simples Nacional - DAS</t>
-  </si>
-  <si>
-    <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
-  </si>
-  <si>
-    <t>22/12/2026</t>
-  </si>
-  <si>
-    <t>64 - 6</t>
-  </si>
-  <si>
-    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
-  </si>
-  <si>
-    <t>25/12/2026</t>
-  </si>
-  <si>
-    <t>68 - 5</t>
-  </si>
-  <si>
-    <t>Luis Carlos Alves de Oliveira</t>
-  </si>
-  <si>
-    <t>26/12/2026</t>
-  </si>
-  <si>
-    <t>EM SOLUCOES INTEGRADAS DE SISTEMAS LTDA ME</t>
-  </si>
-  <si>
-    <t>30/12/2026</t>
-  </si>
-  <si>
     <t>29001 - 14</t>
   </si>
   <si>
@@ -345,7 +330,7 @@
     <t>Total Geral Crédito</t>
   </si>
   <si>
-    <t>23.747,91</t>
+    <t>2.656,53</t>
   </si>
   <si>
     <t>Total Geral Débito</t>
@@ -357,7 +342,7 @@
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-78.697,66</t>
+    <t>-99.789,04</t>
   </si>
 </sst>
 </file>
@@ -425,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H76"/>
+  <dimension ref="A2:H74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -570,10 +555,10 @@
         <v>0.0</v>
       </c>
       <c r="G19" t="n" s="1">
-        <v>808.5</v>
+        <v>15000.0</v>
       </c>
       <c r="H19" t="n" s="1">
-        <v>-808.5</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="20">
@@ -596,10 +581,10 @@
         <v>0.0</v>
       </c>
       <c r="G20" t="n" s="1">
-        <v>15000.0</v>
+        <v>808.5</v>
       </c>
       <c r="H20" t="n" s="1">
-        <v>-15000.0</v>
+        <v>-808.5</v>
       </c>
     </row>
     <row r="21">
@@ -636,22 +621,22 @@
         <v>34</v>
       </c>
       <c r="C22" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D22" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="D22" t="s" s="1">
+      <c r="E22" t="s" s="1">
         <v>36</v>
       </c>
-      <c r="E22" t="s" s="1">
-        <v>37</v>
-      </c>
       <c r="F22" t="n" s="1">
-        <v>4166.67</v>
+        <v>0.0</v>
       </c>
       <c r="G22" t="n" s="1">
-        <v>0.0</v>
+        <v>2536.0</v>
       </c>
       <c r="H22" t="n" s="1">
-        <v>4166.67</v>
+        <v>-2536.0</v>
       </c>
     </row>
     <row r="23">
@@ -659,25 +644,25 @@
         <v>26</v>
       </c>
       <c r="B23" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="E23" t="s" s="1">
         <v>38</v>
       </c>
-      <c r="C23" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="D23" t="s" s="1">
-        <v>39</v>
-      </c>
-      <c r="E23" t="s" s="1">
-        <v>40</v>
-      </c>
       <c r="F23" t="n" s="1">
-        <v>16924.71</v>
+        <v>0.0</v>
       </c>
       <c r="G23" t="n" s="1">
-        <v>0.0</v>
+        <v>2219.85</v>
       </c>
       <c r="H23" t="n" s="1">
-        <v>16924.71</v>
+        <v>-2219.85</v>
       </c>
     </row>
     <row r="24">
@@ -685,25 +670,25 @@
         <v>26</v>
       </c>
       <c r="B24" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D24" t="s" s="1">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s" s="1">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F24" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G24" t="n" s="1">
-        <v>2536.0</v>
+        <v>9.99</v>
       </c>
       <c r="H24" t="n" s="1">
-        <v>-2536.0</v>
+        <v>-9.99</v>
       </c>
     </row>
     <row r="25">
@@ -711,25 +696,25 @@
         <v>26</v>
       </c>
       <c r="B25" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D25" t="s" s="1">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E25" t="s" s="1">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F25" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G25" t="n" s="1">
-        <v>2219.85</v>
+        <v>1000.0</v>
       </c>
       <c r="H25" t="n" s="1">
-        <v>-2219.85</v>
+        <v>-1000.0</v>
       </c>
     </row>
     <row r="26">
@@ -737,25 +722,25 @@
         <v>26</v>
       </c>
       <c r="B26" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D26" t="s" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E26" t="s" s="1">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F26" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G26" t="n" s="1">
-        <v>14250.0</v>
+        <v>2536.0</v>
       </c>
       <c r="H26" t="n" s="1">
-        <v>-14250.0</v>
+        <v>-2536.0</v>
       </c>
     </row>
     <row r="27">
@@ -763,25 +748,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D27" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E27" t="s" s="1">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F27" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G27" t="n" s="1">
-        <v>9.99</v>
+        <v>14250.0</v>
       </c>
       <c r="H27" t="n" s="1">
-        <v>-9.99</v>
+        <v>-14250.0</v>
       </c>
     </row>
     <row r="28">
@@ -789,25 +774,25 @@
         <v>26</v>
       </c>
       <c r="B28" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D28" t="s" s="1">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s" s="1">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F28" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G28" t="n" s="1">
-        <v>1000.0</v>
+        <v>1248.82</v>
       </c>
       <c r="H28" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-1248.82</v>
       </c>
     </row>
     <row r="29">
@@ -815,25 +800,25 @@
         <v>26</v>
       </c>
       <c r="B29" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C29" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D29" t="s" s="1">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E29" t="s" s="1">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F29" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G29" t="n" s="1">
-        <v>2536.0</v>
+        <v>150.0</v>
       </c>
       <c r="H29" t="n" s="1">
-        <v>-2536.0</v>
+        <v>-150.0</v>
       </c>
     </row>
     <row r="30">
@@ -841,25 +826,25 @@
         <v>26</v>
       </c>
       <c r="B30" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D30" t="s" s="1">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E30" t="s" s="1">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F30" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G30" t="n" s="1">
-        <v>1248.82</v>
+        <v>14.99</v>
       </c>
       <c r="H30" t="n" s="1">
-        <v>-1248.82</v>
+        <v>-14.99</v>
       </c>
     </row>
     <row r="31">
@@ -867,7 +852,7 @@
         <v>26</v>
       </c>
       <c r="B31" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s" s="1">
         <v>28</v>
@@ -876,16 +861,16 @@
         <v>29</v>
       </c>
       <c r="E31" t="s" s="1">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F31" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G31" t="n" s="1">
-        <v>1900.0</v>
+        <v>2120.0</v>
       </c>
       <c r="H31" t="n" s="1">
-        <v>-1900.0</v>
+        <v>-2120.0</v>
       </c>
     </row>
     <row r="32">
@@ -893,7 +878,7 @@
         <v>26</v>
       </c>
       <c r="B32" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s" s="1">
         <v>28</v>
@@ -902,16 +887,16 @@
         <v>29</v>
       </c>
       <c r="E32" t="s" s="1">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F32" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G32" t="n" s="1">
-        <v>14.99</v>
+        <v>346.5</v>
       </c>
       <c r="H32" t="n" s="1">
-        <v>-14.99</v>
+        <v>-346.5</v>
       </c>
     </row>
     <row r="33">
@@ -919,7 +904,7 @@
         <v>26</v>
       </c>
       <c r="B33" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s" s="1">
         <v>28</v>
@@ -928,16 +913,16 @@
         <v>29</v>
       </c>
       <c r="E33" t="s" s="1">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F33" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G33" t="n" s="1">
-        <v>2120.0</v>
+        <v>1900.0</v>
       </c>
       <c r="H33" t="n" s="1">
-        <v>-2120.0</v>
+        <v>-1900.0</v>
       </c>
     </row>
     <row r="34">
@@ -945,7 +930,7 @@
         <v>26</v>
       </c>
       <c r="B34" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s" s="1">
         <v>28</v>
@@ -954,16 +939,16 @@
         <v>29</v>
       </c>
       <c r="E34" t="s" s="1">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F34" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G34" t="n" s="1">
-        <v>346.5</v>
+        <v>71.17</v>
       </c>
       <c r="H34" t="n" s="1">
-        <v>-346.5</v>
+        <v>-71.17</v>
       </c>
     </row>
     <row r="35">
@@ -971,7 +956,7 @@
         <v>26</v>
       </c>
       <c r="B35" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s" s="1">
         <v>28</v>
@@ -980,16 +965,16 @@
         <v>29</v>
       </c>
       <c r="E35" t="s" s="1">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F35" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G35" t="n" s="1">
-        <v>1900.0</v>
+        <v>1000.0</v>
       </c>
       <c r="H35" t="n" s="1">
-        <v>-1900.0</v>
+        <v>-1000.0</v>
       </c>
     </row>
     <row r="36">
@@ -997,7 +982,7 @@
         <v>26</v>
       </c>
       <c r="B36" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s" s="1">
         <v>28</v>
@@ -1006,16 +991,16 @@
         <v>29</v>
       </c>
       <c r="E36" t="s" s="1">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F36" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G36" t="n" s="1">
-        <v>71.17</v>
+        <v>1000.0</v>
       </c>
       <c r="H36" t="n" s="1">
-        <v>-71.17</v>
+        <v>-1000.0</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1008,7 @@
         <v>26</v>
       </c>
       <c r="B37" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C37" t="s" s="1">
         <v>28</v>
@@ -1032,16 +1017,16 @@
         <v>29</v>
       </c>
       <c r="E37" t="s" s="1">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F37" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G37" t="n" s="1">
-        <v>1000.0</v>
+        <v>4020.07</v>
       </c>
       <c r="H37" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-4020.07</v>
       </c>
     </row>
     <row r="38">
@@ -1049,7 +1034,7 @@
         <v>26</v>
       </c>
       <c r="B38" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s" s="1">
         <v>28</v>
@@ -1058,16 +1043,16 @@
         <v>29</v>
       </c>
       <c r="E38" t="s" s="1">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F38" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G38" t="n" s="1">
-        <v>1000.0</v>
+        <v>1900.0</v>
       </c>
       <c r="H38" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-1900.0</v>
       </c>
     </row>
     <row r="39">
@@ -1075,7 +1060,7 @@
         <v>26</v>
       </c>
       <c r="B39" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C39" t="s" s="1">
         <v>28</v>
@@ -1084,16 +1069,16 @@
         <v>29</v>
       </c>
       <c r="E39" t="s" s="1">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F39" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G39" t="n" s="1">
-        <v>4020.07</v>
+        <v>49.95</v>
       </c>
       <c r="H39" t="n" s="1">
-        <v>-4020.07</v>
+        <v>-49.95</v>
       </c>
     </row>
     <row r="40">
@@ -1101,7 +1086,7 @@
         <v>26</v>
       </c>
       <c r="B40" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C40" t="s" s="1">
         <v>28</v>
@@ -1110,16 +1095,16 @@
         <v>29</v>
       </c>
       <c r="E40" t="s" s="1">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F40" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G40" t="n" s="1">
-        <v>150.0</v>
+        <v>160.0</v>
       </c>
       <c r="H40" t="n" s="1">
-        <v>-150.0</v>
+        <v>-160.0</v>
       </c>
     </row>
     <row r="41">
@@ -1127,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B41" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C41" t="s" s="1">
         <v>28</v>
@@ -1136,16 +1121,16 @@
         <v>29</v>
       </c>
       <c r="E41" t="s" s="1">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F41" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G41" t="n" s="1">
-        <v>49.95</v>
+        <v>1800.0</v>
       </c>
       <c r="H41" t="n" s="1">
-        <v>-49.95</v>
+        <v>-1800.0</v>
       </c>
     </row>
     <row r="42">
@@ -1153,7 +1138,7 @@
         <v>26</v>
       </c>
       <c r="B42" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C42" t="s" s="1">
         <v>28</v>
@@ -1162,16 +1147,16 @@
         <v>29</v>
       </c>
       <c r="E42" t="s" s="1">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F42" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G42" t="n" s="1">
-        <v>160.0</v>
+        <v>2479.65</v>
       </c>
       <c r="H42" t="n" s="1">
-        <v>-160.0</v>
+        <v>-2479.65</v>
       </c>
     </row>
     <row r="43">
@@ -1179,7 +1164,7 @@
         <v>26</v>
       </c>
       <c r="B43" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s" s="1">
         <v>28</v>
@@ -1188,16 +1173,16 @@
         <v>29</v>
       </c>
       <c r="E43" t="s" s="1">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F43" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G43" t="n" s="1">
-        <v>1800.0</v>
+        <v>6000.0</v>
       </c>
       <c r="H43" t="n" s="1">
-        <v>-1800.0</v>
+        <v>-6000.0</v>
       </c>
     </row>
     <row r="44">
@@ -1205,25 +1190,25 @@
         <v>26</v>
       </c>
       <c r="B44" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C44" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D44" t="s" s="1">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="E44" t="s" s="1">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F44" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G44" t="n" s="1">
-        <v>2479.65</v>
+        <v>94.5</v>
       </c>
       <c r="H44" t="n" s="1">
-        <v>-2479.65</v>
+        <v>-94.5</v>
       </c>
     </row>
     <row r="45">
@@ -1231,25 +1216,25 @@
         <v>26</v>
       </c>
       <c r="B45" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C45" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D45" t="s" s="1">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="E45" t="s" s="1">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="F45" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G45" t="n" s="1">
-        <v>6000.0</v>
+        <v>293.21</v>
       </c>
       <c r="H45" t="n" s="1">
-        <v>-6000.0</v>
+        <v>-293.21</v>
       </c>
     </row>
     <row r="46">
@@ -1257,25 +1242,25 @@
         <v>26</v>
       </c>
       <c r="B46" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C46" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D46" t="s" s="1">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E46" t="s" s="1">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="F46" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G46" t="n" s="1">
-        <v>94.5</v>
+        <v>376.44</v>
       </c>
       <c r="H46" t="n" s="1">
-        <v>-94.5</v>
+        <v>-376.44</v>
       </c>
     </row>
     <row r="47">
@@ -1283,25 +1268,25 @@
         <v>26</v>
       </c>
       <c r="B47" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C47" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D47" t="s" s="1">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E47" t="s" s="1">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F47" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G47" t="n" s="1">
-        <v>293.21</v>
+        <v>114.5</v>
       </c>
       <c r="H47" t="n" s="1">
-        <v>-293.21</v>
+        <v>-114.5</v>
       </c>
     </row>
     <row r="48">
@@ -1309,25 +1294,25 @@
         <v>26</v>
       </c>
       <c r="B48" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C48" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D48" t="s" s="1">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E48" t="s" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F48" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G48" t="n" s="1">
-        <v>376.44</v>
+        <v>188.22</v>
       </c>
       <c r="H48" t="n" s="1">
-        <v>-376.44</v>
+        <v>-188.22</v>
       </c>
     </row>
     <row r="49">
@@ -1335,25 +1320,25 @@
         <v>26</v>
       </c>
       <c r="B49" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C49" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D49" t="s" s="1">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E49" t="s" s="1">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F49" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G49" t="n" s="1">
-        <v>114.5</v>
+        <v>51.58</v>
       </c>
       <c r="H49" t="n" s="1">
-        <v>-114.5</v>
+        <v>-51.58</v>
       </c>
     </row>
     <row r="50">
@@ -1361,25 +1346,25 @@
         <v>26</v>
       </c>
       <c r="B50" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C50" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D50" t="s" s="1">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E50" t="s" s="1">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F50" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G50" t="n" s="1">
-        <v>188.22</v>
+        <v>56.29</v>
       </c>
       <c r="H50" t="n" s="1">
-        <v>-188.22</v>
+        <v>-56.29</v>
       </c>
     </row>
     <row r="51">
@@ -1387,25 +1372,25 @@
         <v>26</v>
       </c>
       <c r="B51" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C51" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D51" t="s" s="1">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E51" t="s" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F51" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G51" t="n" s="1">
-        <v>51.58</v>
+        <v>100.31</v>
       </c>
       <c r="H51" t="n" s="1">
-        <v>-51.58</v>
+        <v>-100.31</v>
       </c>
     </row>
     <row r="52">
@@ -1413,25 +1398,25 @@
         <v>26</v>
       </c>
       <c r="B52" t="s" s="1">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C52" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D52" t="s" s="1">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="E52" t="s" s="1">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F52" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G52" t="n" s="1">
-        <v>56.29</v>
+        <v>599.0</v>
       </c>
       <c r="H52" t="n" s="1">
-        <v>-56.29</v>
+        <v>-599.0</v>
       </c>
     </row>
     <row r="53">
@@ -1439,25 +1424,25 @@
         <v>26</v>
       </c>
       <c r="B53" t="s" s="1">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="C53" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D53" t="s" s="1">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="E53" t="s" s="1">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F53" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G53" t="n" s="1">
-        <v>100.31</v>
+        <v>968.0</v>
       </c>
       <c r="H53" t="n" s="1">
-        <v>-100.31</v>
+        <v>-968.0</v>
       </c>
     </row>
     <row r="54">
@@ -1465,25 +1450,25 @@
         <v>26</v>
       </c>
       <c r="B54" t="s" s="1">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C54" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D54" t="s" s="1">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E54" t="s" s="1">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="F54" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G54" t="n" s="1">
-        <v>599.0</v>
+        <v>4.16</v>
       </c>
       <c r="H54" t="n" s="1">
-        <v>-599.0</v>
+        <v>-4.16</v>
       </c>
     </row>
     <row r="55">
@@ -1491,25 +1476,25 @@
         <v>26</v>
       </c>
       <c r="B55" t="s" s="1">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C55" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D55" t="s" s="1">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="E55" t="s" s="1">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F55" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G55" t="n" s="1">
-        <v>968.0</v>
+        <v>750.0</v>
       </c>
       <c r="H55" t="n" s="1">
-        <v>-968.0</v>
+        <v>-750.0</v>
       </c>
     </row>
     <row r="56">
@@ -1523,19 +1508,19 @@
         <v>28</v>
       </c>
       <c r="D56" t="s" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E56" t="s" s="1">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F56" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G56" t="n" s="1">
-        <v>4.16</v>
+        <v>4588.5</v>
       </c>
       <c r="H56" t="n" s="1">
-        <v>-4.16</v>
+        <v>-4588.5</v>
       </c>
     </row>
     <row r="57">
@@ -1543,25 +1528,25 @@
         <v>26</v>
       </c>
       <c r="B57" t="s" s="1">
+        <v>79</v>
+      </c>
+      <c r="C57" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D57" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="E57" t="s" s="1">
         <v>82</v>
       </c>
-      <c r="C57" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D57" t="s" s="1">
-        <v>83</v>
-      </c>
-      <c r="E57" t="s" s="1">
-        <v>84</v>
-      </c>
       <c r="F57" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G57" t="n" s="1">
-        <v>750.0</v>
+        <v>239.58</v>
       </c>
       <c r="H57" t="n" s="1">
-        <v>-750.0</v>
+        <v>-239.58</v>
       </c>
     </row>
     <row r="58">
@@ -1569,25 +1554,25 @@
         <v>26</v>
       </c>
       <c r="B58" t="s" s="1">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C58" t="s" s="1">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="D58" t="s" s="1">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E58" t="s" s="1">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F58" t="n" s="1">
-        <v>0.0</v>
+        <v>840.0</v>
       </c>
       <c r="G58" t="n" s="1">
-        <v>4588.5</v>
+        <v>0.0</v>
       </c>
       <c r="H58" t="n" s="1">
-        <v>-4588.5</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="59">
@@ -1601,19 +1586,19 @@
         <v>28</v>
       </c>
       <c r="D59" t="s" s="1">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="E59" t="s" s="1">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F59" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G59" t="n" s="1">
-        <v>239.58</v>
+        <v>1500.0</v>
       </c>
       <c r="H59" t="n" s="1">
-        <v>-239.58</v>
+        <v>-1500.0</v>
       </c>
     </row>
     <row r="60">
@@ -1624,22 +1609,22 @@
         <v>85</v>
       </c>
       <c r="C60" t="s" s="1">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="D60" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E60" t="s" s="1">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F60" t="n" s="1">
-        <v>840.0</v>
+        <v>0.0</v>
       </c>
       <c r="G60" t="n" s="1">
-        <v>0.0</v>
+        <v>4500.0</v>
       </c>
       <c r="H60" t="n" s="1">
-        <v>840.0</v>
+        <v>-4500.0</v>
       </c>
     </row>
     <row r="61">
@@ -1647,25 +1632,25 @@
         <v>26</v>
       </c>
       <c r="B61" t="s" s="1">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C61" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D61" t="s" s="1">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E61" t="s" s="1">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F61" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G61" t="n" s="1">
-        <v>1500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="H61" t="n" s="1">
-        <v>-1500.0</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="62">
@@ -1673,25 +1658,25 @@
         <v>26</v>
       </c>
       <c r="B62" t="s" s="1">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C62" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D62" t="s" s="1">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E62" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F62" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G62" t="n" s="1">
-        <v>4500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="H62" t="n" s="1">
-        <v>-4500.0</v>
+        <v>-2000.0</v>
       </c>
     </row>
     <row r="63">
@@ -1699,25 +1684,25 @@
         <v>26</v>
       </c>
       <c r="B63" t="s" s="1">
+        <v>90</v>
+      </c>
+      <c r="C63" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D63" t="s" s="1">
         <v>91</v>
       </c>
-      <c r="C63" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D63" t="s" s="1">
-        <v>45</v>
-      </c>
       <c r="E63" t="s" s="1">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F63" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G63" t="n" s="1">
-        <v>15000.0</v>
+        <v>146.67</v>
       </c>
       <c r="H63" t="n" s="1">
-        <v>-15000.0</v>
+        <v>-146.67</v>
       </c>
     </row>
     <row r="64">
@@ -1725,25 +1710,25 @@
         <v>26</v>
       </c>
       <c r="B64" t="s" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C64" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D64" t="s" s="1">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="E64" t="s" s="1">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="F64" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G64" t="n" s="1">
-        <v>2000.0</v>
+        <v>180.06</v>
       </c>
       <c r="H64" t="n" s="1">
-        <v>-2000.0</v>
+        <v>-180.06</v>
       </c>
     </row>
     <row r="65">
@@ -1751,25 +1736,25 @@
         <v>26</v>
       </c>
       <c r="B65" t="s" s="1">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C65" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D65" t="s" s="1">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E65" t="s" s="1">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F65" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G65" t="n" s="1">
-        <v>146.67</v>
+        <v>1925.0</v>
       </c>
       <c r="H65" t="n" s="1">
-        <v>-146.67</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="66">
@@ -1777,25 +1762,25 @@
         <v>26</v>
       </c>
       <c r="B66" t="s" s="1">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C66" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D66" t="s" s="1">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E66" t="s" s="1">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="F66" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G66" t="n" s="1">
-        <v>180.06</v>
+        <v>1201.89</v>
       </c>
       <c r="H66" t="n" s="1">
-        <v>-180.06</v>
+        <v>-1201.89</v>
       </c>
     </row>
     <row r="67">
@@ -1803,10 +1788,10 @@
         <v>26</v>
       </c>
       <c r="B67" t="s" s="1">
+        <v>98</v>
+      </c>
+      <c r="C67" t="s" s="1">
         <v>99</v>
-      </c>
-      <c r="C67" t="s" s="1">
-        <v>28</v>
       </c>
       <c r="D67" t="s" s="1">
         <v>100</v>
@@ -1815,13 +1800,13 @@
         <v>101</v>
       </c>
       <c r="F67" t="n" s="1">
-        <v>0.0</v>
+        <v>1816.53</v>
       </c>
       <c r="G67" t="n" s="1">
-        <v>1925.0</v>
+        <v>0.0</v>
       </c>
       <c r="H67" t="n" s="1">
-        <v>-1925.0</v>
+        <v>1816.53</v>
       </c>
     </row>
     <row r="68">
@@ -1829,25 +1814,25 @@
         <v>26</v>
       </c>
       <c r="B68" t="s" s="1">
+        <v>98</v>
+      </c>
+      <c r="C68" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D68" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="E68" t="s" s="1">
         <v>102</v>
       </c>
-      <c r="C68" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D68" t="s" s="1">
-        <v>83</v>
-      </c>
-      <c r="E68" t="s" s="1">
-        <v>103</v>
-      </c>
       <c r="F68" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G68" t="n" s="1">
-        <v>1201.89</v>
+        <v>1000.0</v>
       </c>
       <c r="H68" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-1000.0</v>
       </c>
     </row>
     <row r="69">
@@ -1855,101 +1840,49 @@
         <v>26</v>
       </c>
       <c r="B69" t="s" s="1">
+        <v>98</v>
+      </c>
+      <c r="C69" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D69" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E69" t="s" s="1">
+        <v>103</v>
+      </c>
+      <c r="F69" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G69" t="n" s="1">
+        <v>3750.0</v>
+      </c>
+      <c r="H69" t="n" s="1">
+        <v>-3750.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C69" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="D69" t="s" s="1">
+      <c r="B72" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E69" t="s" s="1">
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F69" t="n" s="1">
-        <v>1816.53</v>
-      </c>
-      <c r="G69" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H69" t="n" s="1">
-        <v>1816.53</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B70" t="s" s="1">
-        <v>104</v>
-      </c>
-      <c r="C70" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D70" t="s" s="1">
-        <v>41</v>
-      </c>
-      <c r="E70" t="s" s="1">
+      <c r="B73" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="F70" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G70" t="n" s="1">
-        <v>1000.0</v>
-      </c>
-      <c r="H70" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B71" t="s" s="1">
-        <v>104</v>
-      </c>
-      <c r="C71" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D71" t="s" s="1">
-        <v>45</v>
-      </c>
-      <c r="E71" t="s" s="1">
-        <v>108</v>
-      </c>
-      <c r="F71" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G71" t="n" s="1">
-        <v>3750.0</v>
-      </c>
-      <c r="H71" t="n" s="1">
-        <v>-3750.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="111">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -252,6 +252,18 @@
     <t>Enel</t>
   </si>
   <si>
+    <t>15/12/2026</t>
+  </si>
+  <si>
+    <t>DUP-Duplicata de Contrato</t>
+  </si>
+  <si>
+    <t>29001 - 13</t>
+  </si>
+  <si>
+    <t>GABRIEL DE CARVALHO MELLO</t>
+  </si>
+  <si>
     <t>18/12/2026</t>
   </si>
   <si>
@@ -273,18 +285,18 @@
     <t>20/12/2026</t>
   </si>
   <si>
+    <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
+  </si>
+  <si>
+    <t>IRRF- darf</t>
+  </si>
+  <si>
+    <t>Simples Nacional - DAS</t>
+  </si>
+  <si>
     <t>INSS- Previdenciária</t>
   </si>
   <si>
-    <t>IRRF- darf</t>
-  </si>
-  <si>
-    <t>Simples Nacional - DAS</t>
-  </si>
-  <si>
-    <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
-  </si>
-  <si>
     <t>22/12/2026</t>
   </si>
   <si>
@@ -310,15 +322,6 @@
   </si>
   <si>
     <t>30/12/2026</t>
-  </si>
-  <si>
-    <t>DUP-Duplicata de Contrato</t>
-  </si>
-  <si>
-    <t>29001 - 14</t>
-  </si>
-  <si>
-    <t>GABRIEL DE CARVALHO MELLO</t>
   </si>
   <si>
     <t>SEFAZ SP DARE - ICMS</t>
@@ -1505,22 +1508,22 @@
         <v>79</v>
       </c>
       <c r="C56" t="s" s="1">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D56" t="s" s="1">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="E56" t="s" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F56" t="n" s="1">
-        <v>0.0</v>
+        <v>1816.53</v>
       </c>
       <c r="G56" t="n" s="1">
-        <v>4588.5</v>
+        <v>0.0</v>
       </c>
       <c r="H56" t="n" s="1">
-        <v>-4588.5</v>
+        <v>1816.53</v>
       </c>
     </row>
     <row r="57">
@@ -1528,25 +1531,25 @@
         <v>26</v>
       </c>
       <c r="B57" t="s" s="1">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C57" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D57" t="s" s="1">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="E57" t="s" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F57" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G57" t="n" s="1">
-        <v>239.58</v>
+        <v>4588.5</v>
       </c>
       <c r="H57" t="n" s="1">
-        <v>-239.58</v>
+        <v>-4588.5</v>
       </c>
     </row>
     <row r="58">
@@ -1554,25 +1557,25 @@
         <v>26</v>
       </c>
       <c r="B58" t="s" s="1">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C58" t="s" s="1">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="D58" t="s" s="1">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="E58" t="s" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F58" t="n" s="1">
-        <v>840.0</v>
+        <v>0.0</v>
       </c>
       <c r="G58" t="n" s="1">
-        <v>0.0</v>
+        <v>239.58</v>
       </c>
       <c r="H58" t="n" s="1">
-        <v>840.0</v>
+        <v>-239.58</v>
       </c>
     </row>
     <row r="59">
@@ -1580,25 +1583,25 @@
         <v>26</v>
       </c>
       <c r="B59" t="s" s="1">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C59" t="s" s="1">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="D59" t="s" s="1">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E59" t="s" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F59" t="n" s="1">
-        <v>0.0</v>
+        <v>840.0</v>
       </c>
       <c r="G59" t="n" s="1">
-        <v>1500.0</v>
+        <v>0.0</v>
       </c>
       <c r="H59" t="n" s="1">
-        <v>-1500.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="60">
@@ -1606,7 +1609,7 @@
         <v>26</v>
       </c>
       <c r="B60" t="s" s="1">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C60" t="s" s="1">
         <v>28</v>
@@ -1615,16 +1618,16 @@
         <v>42</v>
       </c>
       <c r="E60" t="s" s="1">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F60" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G60" t="n" s="1">
-        <v>4500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="H60" t="n" s="1">
-        <v>-4500.0</v>
+        <v>-2000.0</v>
       </c>
     </row>
     <row r="61">
@@ -1632,7 +1635,7 @@
         <v>26</v>
       </c>
       <c r="B61" t="s" s="1">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C61" t="s" s="1">
         <v>28</v>
@@ -1641,16 +1644,16 @@
         <v>42</v>
       </c>
       <c r="E61" t="s" s="1">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F61" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G61" t="n" s="1">
-        <v>15000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="H61" t="n" s="1">
-        <v>-15000.0</v>
+        <v>-4500.0</v>
       </c>
     </row>
     <row r="62">
@@ -1658,7 +1661,7 @@
         <v>26</v>
       </c>
       <c r="B62" t="s" s="1">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C62" t="s" s="1">
         <v>28</v>
@@ -1667,16 +1670,16 @@
         <v>42</v>
       </c>
       <c r="E62" t="s" s="1">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F62" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G62" t="n" s="1">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="H62" t="n" s="1">
-        <v>-2000.0</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="63">
@@ -1684,25 +1687,25 @@
         <v>26</v>
       </c>
       <c r="B63" t="s" s="1">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C63" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D63" t="s" s="1">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="E63" t="s" s="1">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F63" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G63" t="n" s="1">
-        <v>146.67</v>
+        <v>1500.0</v>
       </c>
       <c r="H63" t="n" s="1">
-        <v>-146.67</v>
+        <v>-1500.0</v>
       </c>
     </row>
     <row r="64">
@@ -1710,25 +1713,25 @@
         <v>26</v>
       </c>
       <c r="B64" t="s" s="1">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C64" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D64" t="s" s="1">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="E64" t="s" s="1">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="F64" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G64" t="n" s="1">
-        <v>180.06</v>
+        <v>146.67</v>
       </c>
       <c r="H64" t="n" s="1">
-        <v>-180.06</v>
+        <v>-146.67</v>
       </c>
     </row>
     <row r="65">
@@ -1736,25 +1739,25 @@
         <v>26</v>
       </c>
       <c r="B65" t="s" s="1">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C65" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D65" t="s" s="1">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="E65" t="s" s="1">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="F65" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G65" t="n" s="1">
-        <v>1925.0</v>
+        <v>180.06</v>
       </c>
       <c r="H65" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-180.06</v>
       </c>
     </row>
     <row r="66">
@@ -1762,25 +1765,25 @@
         <v>26</v>
       </c>
       <c r="B66" t="s" s="1">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C66" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D66" t="s" s="1">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="E66" t="s" s="1">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F66" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G66" t="n" s="1">
-        <v>1201.89</v>
+        <v>1925.0</v>
       </c>
       <c r="H66" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="67">
@@ -1788,25 +1791,25 @@
         <v>26</v>
       </c>
       <c r="B67" t="s" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C67" t="s" s="1">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="D67" t="s" s="1">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="E67" t="s" s="1">
         <v>101</v>
       </c>
       <c r="F67" t="n" s="1">
-        <v>1816.53</v>
+        <v>0.0</v>
       </c>
       <c r="G67" t="n" s="1">
-        <v>0.0</v>
+        <v>1201.89</v>
       </c>
       <c r="H67" t="n" s="1">
-        <v>1816.53</v>
+        <v>-1201.89</v>
       </c>
     </row>
     <row r="68">
@@ -1814,7 +1817,7 @@
         <v>26</v>
       </c>
       <c r="B68" t="s" s="1">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C68" t="s" s="1">
         <v>28</v>
@@ -1823,7 +1826,7 @@
         <v>35</v>
       </c>
       <c r="E68" t="s" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F68" t="n" s="1">
         <v>0.0</v>
@@ -1840,7 +1843,7 @@
         <v>26</v>
       </c>
       <c r="B69" t="s" s="1">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C69" t="s" s="1">
         <v>28</v>
@@ -1849,7 +1852,7 @@
         <v>42</v>
       </c>
       <c r="E69" t="s" s="1">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F69" t="n" s="1">
         <v>0.0</v>
@@ -1863,26 +1866,26 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="114">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -123,6 +123,9 @@
     <t>1 - 10</t>
   </si>
   <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
     <t>BIANCA RODRIGUES</t>
   </si>
   <si>
@@ -138,9 +141,6 @@
     <t>FERNANDA DOCHVAT SILVA</t>
   </si>
   <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
     <t>1 - 11</t>
   </si>
   <si>
@@ -153,36 +153,36 @@
     <t>Promob</t>
   </si>
   <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>FERNANDO OLIVEIRA LEITE</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>SINDICATO DO COM VAREJ E LOJISTA DO COM DE SP - SI</t>
+  </si>
+  <si>
+    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
     <t>Jackson Fernando de Araujo</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>FERNANDO OLIVEIRA LEITE</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>SINDICATO DO COM VAREJ E LOJISTA DO COM DE SP - SI</t>
-  </si>
-  <si>
-    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
     <t>D4 sign</t>
   </si>
   <si>
@@ -237,12 +237,12 @@
     <t>10/12/2026</t>
   </si>
   <si>
+    <t>PREFEITURA SP- ISS</t>
+  </si>
+  <si>
     <t>Roger Duarte Pinheiro Me</t>
   </si>
   <si>
-    <t>PREFEITURA SP- ISS</t>
-  </si>
-  <si>
     <t>12/12/2026</t>
   </si>
   <si>
@@ -264,6 +264,15 @@
     <t>GABRIEL DE CARVALHO MELLO</t>
   </si>
   <si>
+    <t>16/12/2026</t>
+  </si>
+  <si>
+    <t>105101 - 2</t>
+  </si>
+  <si>
+    <t>Claudio Wasserman</t>
+  </si>
+  <si>
     <t>18/12/2026</t>
   </si>
   <si>
@@ -285,15 +294,15 @@
     <t>20/12/2026</t>
   </si>
   <si>
+    <t>Simples Nacional - DAS</t>
+  </si>
+  <si>
+    <t>IRRF- darf</t>
+  </si>
+  <si>
     <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
   </si>
   <si>
-    <t>IRRF- darf</t>
-  </si>
-  <si>
-    <t>Simples Nacional - DAS</t>
-  </si>
-  <si>
     <t>INSS- Previdenciária</t>
   </si>
   <si>
@@ -333,7 +342,7 @@
     <t>Total Geral Crédito</t>
   </si>
   <si>
-    <t>2.656,53</t>
+    <t>12.836,53</t>
   </si>
   <si>
     <t>Total Geral Débito</t>
@@ -345,7 +354,7 @@
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-99.789,04</t>
+    <t>-89.609,04</t>
   </si>
 </sst>
 </file>
@@ -413,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H74"/>
+  <dimension ref="A2:H75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -653,19 +662,19 @@
         <v>28</v>
       </c>
       <c r="D23" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="E23" t="s" s="1">
         <v>37</v>
       </c>
-      <c r="E23" t="s" s="1">
-        <v>38</v>
-      </c>
       <c r="F23" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G23" t="n" s="1">
-        <v>2219.85</v>
+        <v>2536.0</v>
       </c>
       <c r="H23" t="n" s="1">
-        <v>-2219.85</v>
+        <v>-2536.0</v>
       </c>
     </row>
     <row r="24">
@@ -679,7 +688,7 @@
         <v>28</v>
       </c>
       <c r="D24" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E24" t="s" s="1">
         <v>39</v>
@@ -688,10 +697,10 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n" s="1">
-        <v>9.99</v>
+        <v>2219.85</v>
       </c>
       <c r="H24" t="n" s="1">
-        <v>-9.99</v>
+        <v>-2219.85</v>
       </c>
     </row>
     <row r="25">
@@ -714,10 +723,10 @@
         <v>0.0</v>
       </c>
       <c r="G25" t="n" s="1">
-        <v>1000.0</v>
+        <v>9.99</v>
       </c>
       <c r="H25" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-9.99</v>
       </c>
     </row>
     <row r="26">
@@ -740,10 +749,10 @@
         <v>0.0</v>
       </c>
       <c r="G26" t="n" s="1">
-        <v>2536.0</v>
+        <v>1000.0</v>
       </c>
       <c r="H26" t="n" s="1">
-        <v>-2536.0</v>
+        <v>-1000.0</v>
       </c>
     </row>
     <row r="27">
@@ -818,10 +827,10 @@
         <v>0.0</v>
       </c>
       <c r="G29" t="n" s="1">
-        <v>150.0</v>
+        <v>1900.0</v>
       </c>
       <c r="H29" t="n" s="1">
-        <v>-150.0</v>
+        <v>-1900.0</v>
       </c>
     </row>
     <row r="30">
@@ -1052,10 +1061,10 @@
         <v>0.0</v>
       </c>
       <c r="G38" t="n" s="1">
-        <v>1900.0</v>
+        <v>150.0</v>
       </c>
       <c r="H38" t="n" s="1">
-        <v>-1900.0</v>
+        <v>-150.0</v>
       </c>
     </row>
     <row r="39">
@@ -1442,10 +1451,10 @@
         <v>0.0</v>
       </c>
       <c r="G53" t="n" s="1">
-        <v>968.0</v>
+        <v>4.16</v>
       </c>
       <c r="H53" t="n" s="1">
-        <v>-968.0</v>
+        <v>-4.16</v>
       </c>
     </row>
     <row r="54">
@@ -1468,10 +1477,10 @@
         <v>0.0</v>
       </c>
       <c r="G54" t="n" s="1">
-        <v>4.16</v>
+        <v>968.0</v>
       </c>
       <c r="H54" t="n" s="1">
-        <v>-4.16</v>
+        <v>-968.0</v>
       </c>
     </row>
     <row r="55">
@@ -1534,22 +1543,22 @@
         <v>83</v>
       </c>
       <c r="C57" t="s" s="1">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D57" t="s" s="1">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="E57" t="s" s="1">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F57" t="n" s="1">
-        <v>0.0</v>
+        <v>10180.0</v>
       </c>
       <c r="G57" t="n" s="1">
-        <v>4588.5</v>
+        <v>0.0</v>
       </c>
       <c r="H57" t="n" s="1">
-        <v>-4588.5</v>
+        <v>10180.0</v>
       </c>
     </row>
     <row r="58">
@@ -1557,25 +1566,25 @@
         <v>26</v>
       </c>
       <c r="B58" t="s" s="1">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C58" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D58" t="s" s="1">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="E58" t="s" s="1">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F58" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G58" t="n" s="1">
-        <v>239.58</v>
+        <v>4588.5</v>
       </c>
       <c r="H58" t="n" s="1">
-        <v>-239.58</v>
+        <v>-4588.5</v>
       </c>
     </row>
     <row r="59">
@@ -1583,25 +1592,25 @@
         <v>26</v>
       </c>
       <c r="B59" t="s" s="1">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C59" t="s" s="1">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="D59" t="s" s="1">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="E59" t="s" s="1">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F59" t="n" s="1">
-        <v>840.0</v>
+        <v>0.0</v>
       </c>
       <c r="G59" t="n" s="1">
-        <v>0.0</v>
+        <v>239.58</v>
       </c>
       <c r="H59" t="n" s="1">
-        <v>840.0</v>
+        <v>-239.58</v>
       </c>
     </row>
     <row r="60">
@@ -1609,25 +1618,25 @@
         <v>26</v>
       </c>
       <c r="B60" t="s" s="1">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C60" t="s" s="1">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="D60" t="s" s="1">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E60" t="s" s="1">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F60" t="n" s="1">
-        <v>0.0</v>
+        <v>840.0</v>
       </c>
       <c r="G60" t="n" s="1">
-        <v>2000.0</v>
+        <v>0.0</v>
       </c>
       <c r="H60" t="n" s="1">
-        <v>-2000.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="61">
@@ -1635,7 +1644,7 @@
         <v>26</v>
       </c>
       <c r="B61" t="s" s="1">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C61" t="s" s="1">
         <v>28</v>
@@ -1644,16 +1653,16 @@
         <v>42</v>
       </c>
       <c r="E61" t="s" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F61" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G61" t="n" s="1">
-        <v>4500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="H61" t="n" s="1">
-        <v>-4500.0</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="62">
@@ -1661,7 +1670,7 @@
         <v>26</v>
       </c>
       <c r="B62" t="s" s="1">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C62" t="s" s="1">
         <v>28</v>
@@ -1670,16 +1679,16 @@
         <v>42</v>
       </c>
       <c r="E62" t="s" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F62" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G62" t="n" s="1">
-        <v>15000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="H62" t="n" s="1">
-        <v>-15000.0</v>
+        <v>-4500.0</v>
       </c>
     </row>
     <row r="63">
@@ -1687,7 +1696,7 @@
         <v>26</v>
       </c>
       <c r="B63" t="s" s="1">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C63" t="s" s="1">
         <v>28</v>
@@ -1696,16 +1705,16 @@
         <v>42</v>
       </c>
       <c r="E63" t="s" s="1">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F63" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G63" t="n" s="1">
-        <v>1500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="H63" t="n" s="1">
-        <v>-1500.0</v>
+        <v>-2000.0</v>
       </c>
     </row>
     <row r="64">
@@ -1713,13 +1722,13 @@
         <v>26</v>
       </c>
       <c r="B64" t="s" s="1">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D64" t="s" s="1">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="E64" t="s" s="1">
         <v>96</v>
@@ -1728,10 +1737,10 @@
         <v>0.0</v>
       </c>
       <c r="G64" t="n" s="1">
-        <v>146.67</v>
+        <v>1500.0</v>
       </c>
       <c r="H64" t="n" s="1">
-        <v>-146.67</v>
+        <v>-1500.0</v>
       </c>
     </row>
     <row r="65">
@@ -1745,19 +1754,19 @@
         <v>28</v>
       </c>
       <c r="D65" t="s" s="1">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="E65" t="s" s="1">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="F65" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G65" t="n" s="1">
-        <v>180.06</v>
+        <v>146.67</v>
       </c>
       <c r="H65" t="n" s="1">
-        <v>-180.06</v>
+        <v>-146.67</v>
       </c>
     </row>
     <row r="66">
@@ -1765,25 +1774,25 @@
         <v>26</v>
       </c>
       <c r="B66" t="s" s="1">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C66" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D66" t="s" s="1">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="E66" t="s" s="1">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="F66" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G66" t="n" s="1">
-        <v>1925.0</v>
+        <v>180.06</v>
       </c>
       <c r="H66" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-180.06</v>
       </c>
     </row>
     <row r="67">
@@ -1797,19 +1806,19 @@
         <v>28</v>
       </c>
       <c r="D67" t="s" s="1">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E67" t="s" s="1">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F67" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G67" t="n" s="1">
-        <v>1201.89</v>
+        <v>1925.0</v>
       </c>
       <c r="H67" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="68">
@@ -1817,25 +1826,25 @@
         <v>26</v>
       </c>
       <c r="B68" t="s" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C68" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D68" t="s" s="1">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="E68" t="s" s="1">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F68" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G68" t="n" s="1">
-        <v>1000.0</v>
+        <v>1201.89</v>
       </c>
       <c r="H68" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-1201.89</v>
       </c>
     </row>
     <row r="69">
@@ -1843,49 +1852,75 @@
         <v>26</v>
       </c>
       <c r="B69" t="s" s="1">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C69" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D69" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="E69" t="s" s="1">
+        <v>106</v>
+      </c>
+      <c r="F69" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G69" t="n" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="H69" t="n" s="1">
+        <v>-1000.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B70" t="s" s="1">
+        <v>105</v>
+      </c>
+      <c r="C70" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D70" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="E69" t="s" s="1">
-        <v>104</v>
-      </c>
-      <c r="F69" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G69" t="n" s="1">
+      <c r="E70" t="s" s="1">
+        <v>107</v>
+      </c>
+      <c r="F70" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G70" t="n" s="1">
         <v>3750.0</v>
       </c>
-      <c r="H69" t="n" s="1">
+      <c r="H70" t="n" s="1">
         <v>-3750.0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="116">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -126,6 +126,12 @@
     <t>Eric Kevin de Souza Serpa</t>
   </si>
   <si>
+    <t>1 - 11</t>
+  </si>
+  <si>
+    <t>DECORA INTERIORES LTDA</t>
+  </si>
+  <si>
     <t>BIANCA RODRIGUES</t>
   </si>
   <si>
@@ -141,51 +147,45 @@
     <t>FERNANDA DOCHVAT SILVA</t>
   </si>
   <si>
-    <t>1 - 11</t>
-  </si>
-  <si>
-    <t>DECORA INTERIORES LTDA</t>
-  </si>
-  <si>
     <t>3 - 10</t>
   </si>
   <si>
     <t>Promob</t>
   </si>
   <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>FERNANDO OLIVEIRA LEITE</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>SINDICATO DO COM VAREJ E LOJISTA DO COM DE SP - SI</t>
+  </si>
+  <si>
+    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>Jackson Fernando de Araujo</t>
+  </si>
+  <si>
     <t>Danielle Martins da Silva</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>FERNANDO OLIVEIRA LEITE</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>SINDICATO DO COM VAREJ E LOJISTA DO COM DE SP - SI</t>
-  </si>
-  <si>
-    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>Jackson Fernando de Araujo</t>
-  </si>
-  <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
     <t>Sabesp</t>
   </si>
   <si>
@@ -237,12 +237,12 @@
     <t>10/12/2026</t>
   </si>
   <si>
+    <t>Roger Duarte Pinheiro Me</t>
+  </si>
+  <si>
     <t>PREFEITURA SP- ISS</t>
   </si>
   <si>
-    <t>Roger Duarte Pinheiro Me</t>
-  </si>
-  <si>
     <t>12/12/2026</t>
   </si>
   <si>
@@ -276,6 +276,12 @@
     <t>18/12/2026</t>
   </si>
   <si>
+    <t>104401 - 2</t>
+  </si>
+  <si>
+    <t>REGINA RURIKO TATEIGI</t>
+  </si>
+  <si>
     <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
   </si>
   <si>
@@ -294,18 +300,18 @@
     <t>20/12/2026</t>
   </si>
   <si>
+    <t>IRRF- darf</t>
+  </si>
+  <si>
     <t>Simples Nacional - DAS</t>
   </si>
   <si>
-    <t>IRRF- darf</t>
+    <t>INSS- Previdenciária</t>
   </si>
   <si>
     <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
   </si>
   <si>
-    <t>INSS- Previdenciária</t>
-  </si>
-  <si>
     <t>22/12/2026</t>
   </si>
   <si>
@@ -342,7 +348,7 @@
     <t>Total Geral Crédito</t>
   </si>
   <si>
-    <t>12.836,53</t>
+    <t>20.261,53</t>
   </si>
   <si>
     <t>Total Geral Débito</t>
@@ -354,7 +360,7 @@
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-89.609,04</t>
+    <t>-82.184,04</t>
   </si>
 </sst>
 </file>
@@ -422,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H75"/>
+  <dimension ref="A2:H76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -662,19 +668,19 @@
         <v>28</v>
       </c>
       <c r="D23" t="s" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E23" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F23" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G23" t="n" s="1">
-        <v>2536.0</v>
+        <v>14250.0</v>
       </c>
       <c r="H23" t="n" s="1">
-        <v>-2536.0</v>
+        <v>-14250.0</v>
       </c>
     </row>
     <row r="24">
@@ -688,7 +694,7 @@
         <v>28</v>
       </c>
       <c r="D24" t="s" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s" s="1">
         <v>39</v>
@@ -697,10 +703,10 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n" s="1">
-        <v>2219.85</v>
+        <v>2536.0</v>
       </c>
       <c r="H24" t="n" s="1">
-        <v>-2219.85</v>
+        <v>-2536.0</v>
       </c>
     </row>
     <row r="25">
@@ -714,19 +720,19 @@
         <v>28</v>
       </c>
       <c r="D25" t="s" s="1">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E25" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F25" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G25" t="n" s="1">
-        <v>9.99</v>
+        <v>2219.85</v>
       </c>
       <c r="H25" t="n" s="1">
-        <v>-9.99</v>
+        <v>-2219.85</v>
       </c>
     </row>
     <row r="26">
@@ -743,16 +749,16 @@
         <v>35</v>
       </c>
       <c r="E26" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F26" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G26" t="n" s="1">
-        <v>1000.0</v>
+        <v>9.99</v>
       </c>
       <c r="H26" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-9.99</v>
       </c>
     </row>
     <row r="27">
@@ -766,7 +772,7 @@
         <v>28</v>
       </c>
       <c r="D27" t="s" s="1">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E27" t="s" s="1">
         <v>43</v>
@@ -775,10 +781,10 @@
         <v>0.0</v>
       </c>
       <c r="G27" t="n" s="1">
-        <v>14250.0</v>
+        <v>1000.0</v>
       </c>
       <c r="H27" t="n" s="1">
-        <v>-14250.0</v>
+        <v>-1000.0</v>
       </c>
     </row>
     <row r="28">
@@ -827,10 +833,10 @@
         <v>0.0</v>
       </c>
       <c r="G29" t="n" s="1">
-        <v>1900.0</v>
+        <v>49.95</v>
       </c>
       <c r="H29" t="n" s="1">
-        <v>-1900.0</v>
+        <v>-49.95</v>
       </c>
     </row>
     <row r="30">
@@ -1087,10 +1093,10 @@
         <v>0.0</v>
       </c>
       <c r="G39" t="n" s="1">
-        <v>49.95</v>
+        <v>1900.0</v>
       </c>
       <c r="H39" t="n" s="1">
-        <v>-49.95</v>
+        <v>-1900.0</v>
       </c>
     </row>
     <row r="40">
@@ -1442,7 +1448,7 @@
         <v>28</v>
       </c>
       <c r="D53" t="s" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E53" t="s" s="1">
         <v>74</v>
@@ -1451,10 +1457,10 @@
         <v>0.0</v>
       </c>
       <c r="G53" t="n" s="1">
-        <v>4.16</v>
+        <v>968.0</v>
       </c>
       <c r="H53" t="n" s="1">
-        <v>-4.16</v>
+        <v>-968.0</v>
       </c>
     </row>
     <row r="54">
@@ -1468,7 +1474,7 @@
         <v>28</v>
       </c>
       <c r="D54" t="s" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E54" t="s" s="1">
         <v>75</v>
@@ -1477,10 +1483,10 @@
         <v>0.0</v>
       </c>
       <c r="G54" t="n" s="1">
-        <v>968.0</v>
+        <v>4.16</v>
       </c>
       <c r="H54" t="n" s="1">
-        <v>-968.0</v>
+        <v>-4.16</v>
       </c>
     </row>
     <row r="55">
@@ -1569,22 +1575,22 @@
         <v>86</v>
       </c>
       <c r="C58" t="s" s="1">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D58" t="s" s="1">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="E58" t="s" s="1">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F58" t="n" s="1">
-        <v>0.0</v>
+        <v>7425.0</v>
       </c>
       <c r="G58" t="n" s="1">
-        <v>4588.5</v>
+        <v>0.0</v>
       </c>
       <c r="H58" t="n" s="1">
-        <v>-4588.5</v>
+        <v>7425.0</v>
       </c>
     </row>
     <row r="59">
@@ -1598,7 +1604,7 @@
         <v>28</v>
       </c>
       <c r="D59" t="s" s="1">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="E59" t="s" s="1">
         <v>89</v>
@@ -1607,10 +1613,10 @@
         <v>0.0</v>
       </c>
       <c r="G59" t="n" s="1">
-        <v>239.58</v>
+        <v>4588.5</v>
       </c>
       <c r="H59" t="n" s="1">
-        <v>-239.58</v>
+        <v>-4588.5</v>
       </c>
     </row>
     <row r="60">
@@ -1621,22 +1627,22 @@
         <v>86</v>
       </c>
       <c r="C60" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D60" t="s" s="1">
         <v>90</v>
-      </c>
-      <c r="D60" t="s" s="1">
-        <v>35</v>
       </c>
       <c r="E60" t="s" s="1">
         <v>91</v>
       </c>
       <c r="F60" t="n" s="1">
-        <v>840.0</v>
+        <v>0.0</v>
       </c>
       <c r="G60" t="n" s="1">
-        <v>0.0</v>
+        <v>239.58</v>
       </c>
       <c r="H60" t="n" s="1">
-        <v>840.0</v>
+        <v>-239.58</v>
       </c>
     </row>
     <row r="61">
@@ -1644,25 +1650,25 @@
         <v>26</v>
       </c>
       <c r="B61" t="s" s="1">
+        <v>86</v>
+      </c>
+      <c r="C61" t="s" s="1">
         <v>92</v>
       </c>
-      <c r="C61" t="s" s="1">
-        <v>28</v>
-      </c>
       <c r="D61" t="s" s="1">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E61" t="s" s="1">
         <v>93</v>
       </c>
       <c r="F61" t="n" s="1">
-        <v>0.0</v>
+        <v>840.0</v>
       </c>
       <c r="G61" t="n" s="1">
-        <v>15000.0</v>
+        <v>0.0</v>
       </c>
       <c r="H61" t="n" s="1">
-        <v>-15000.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="62">
@@ -1670,16 +1676,16 @@
         <v>26</v>
       </c>
       <c r="B62" t="s" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C62" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D62" t="s" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E62" t="s" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F62" t="n" s="1">
         <v>0.0</v>
@@ -1696,25 +1702,25 @@
         <v>26</v>
       </c>
       <c r="B63" t="s" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C63" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D63" t="s" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E63" t="s" s="1">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F63" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G63" t="n" s="1">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="H63" t="n" s="1">
-        <v>-2000.0</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="64">
@@ -1722,16 +1728,16 @@
         <v>26</v>
       </c>
       <c r="B64" t="s" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C64" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D64" t="s" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E64" t="s" s="1">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F64" t="n" s="1">
         <v>0.0</v>
@@ -1748,25 +1754,25 @@
         <v>26</v>
       </c>
       <c r="B65" t="s" s="1">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C65" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D65" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="E65" t="s" s="1">
         <v>98</v>
       </c>
-      <c r="E65" t="s" s="1">
-        <v>99</v>
-      </c>
       <c r="F65" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G65" t="n" s="1">
-        <v>146.67</v>
+        <v>2000.0</v>
       </c>
       <c r="H65" t="n" s="1">
-        <v>-146.67</v>
+        <v>-2000.0</v>
       </c>
     </row>
     <row r="66">
@@ -1774,25 +1780,25 @@
         <v>26</v>
       </c>
       <c r="B66" t="s" s="1">
+        <v>99</v>
+      </c>
+      <c r="C66" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D66" t="s" s="1">
         <v>100</v>
       </c>
-      <c r="C66" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D66" t="s" s="1">
-        <v>77</v>
-      </c>
       <c r="E66" t="s" s="1">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="F66" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G66" t="n" s="1">
-        <v>180.06</v>
+        <v>146.67</v>
       </c>
       <c r="H66" t="n" s="1">
-        <v>-180.06</v>
+        <v>-146.67</v>
       </c>
     </row>
     <row r="67">
@@ -1800,25 +1806,25 @@
         <v>26</v>
       </c>
       <c r="B67" t="s" s="1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C67" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D67" t="s" s="1">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="E67" t="s" s="1">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="F67" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G67" t="n" s="1">
-        <v>1925.0</v>
+        <v>180.06</v>
       </c>
       <c r="H67" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-180.06</v>
       </c>
     </row>
     <row r="68">
@@ -1826,13 +1832,13 @@
         <v>26</v>
       </c>
       <c r="B68" t="s" s="1">
+        <v>102</v>
+      </c>
+      <c r="C68" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D68" t="s" s="1">
         <v>103</v>
-      </c>
-      <c r="C68" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D68" t="s" s="1">
-        <v>77</v>
       </c>
       <c r="E68" t="s" s="1">
         <v>104</v>
@@ -1841,10 +1847,10 @@
         <v>0.0</v>
       </c>
       <c r="G68" t="n" s="1">
-        <v>1201.89</v>
+        <v>1925.0</v>
       </c>
       <c r="H68" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="69">
@@ -1858,7 +1864,7 @@
         <v>28</v>
       </c>
       <c r="D69" t="s" s="1">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="E69" t="s" s="1">
         <v>106</v>
@@ -1867,10 +1873,10 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n" s="1">
-        <v>1000.0</v>
+        <v>1201.89</v>
       </c>
       <c r="H69" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-1201.89</v>
       </c>
     </row>
     <row r="70">
@@ -1878,33 +1884,51 @@
         <v>26</v>
       </c>
       <c r="B70" t="s" s="1">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C70" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D70" t="s" s="1">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E70" t="s" s="1">
+        <v>108</v>
+      </c>
+      <c r="F70" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G70" t="n" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="H70" t="n" s="1">
+        <v>-1000.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B71" t="s" s="1">
         <v>107</v>
       </c>
-      <c r="F70" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G70" t="n" s="1">
+      <c r="C71" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D71" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="E71" t="s" s="1">
+        <v>109</v>
+      </c>
+      <c r="F71" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G71" t="n" s="1">
         <v>3750.0</v>
       </c>
-      <c r="H70" t="n" s="1">
+      <c r="H71" t="n" s="1">
         <v>-3750.0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="74">
@@ -1921,6 +1945,14 @@
       </c>
       <c r="B75" s="3" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="120">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -126,78 +126,78 @@
     <t>Eric Kevin de Souza Serpa</t>
   </si>
   <si>
+    <t>bianca rodrigues</t>
+  </si>
+  <si>
+    <t>1 - 9</t>
+  </si>
+  <si>
+    <t>FELIPE DOMINGOS BARBOSA</t>
+  </si>
+  <si>
+    <t>Hostgator</t>
+  </si>
+  <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
     <t>1 - 11</t>
   </si>
   <si>
     <t>DECORA INTERIORES LTDA</t>
   </si>
   <si>
-    <t>BIANCA RODRIGUES</t>
-  </si>
-  <si>
-    <t>1 - 9</t>
-  </si>
-  <si>
-    <t>FELIPE DOMINGOS BARBOSA</t>
-  </si>
-  <si>
-    <t>Hostgator</t>
-  </si>
-  <si>
-    <t>FERNANDA DOCHVAT SILVA</t>
-  </si>
-  <si>
     <t>3 - 10</t>
   </si>
   <si>
     <t>Promob</t>
   </si>
   <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>FERNANDO OLIVEIRA LEITE</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>SINDICATO DO COM VAREJ E LOJISTA DO COM DE SP - SI</t>
+  </si>
+  <si>
+    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Jackson Fernando de Araujo</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
     <t>D4 sign</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>FERNANDO OLIVEIRA LEITE</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>SINDICATO DO COM VAREJ E LOJISTA DO COM DE SP - SI</t>
-  </si>
-  <si>
-    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>Jackson Fernando de Araujo</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>Thais Pereira Pires</t>
   </si>
   <si>
     <t>Sabesp</t>
   </si>
   <si>
-    <t>Thais Pereira Pires</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
     <t>61 - 7</t>
   </si>
   <si>
@@ -231,18 +231,39 @@
     <t>MP  MARKFERRAGENS</t>
   </si>
   <si>
+    <t>76 - 2</t>
+  </si>
+  <si>
+    <t>Shopee</t>
+  </si>
+  <si>
+    <t>77 - 2</t>
+  </si>
+  <si>
+    <t>78 - 2</t>
+  </si>
+  <si>
+    <t>EFRAIM RIBEIRO</t>
+  </si>
+  <si>
+    <t>79 - 2</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
     <t>08/12/2026</t>
   </si>
   <si>
     <t>10/12/2026</t>
   </si>
   <si>
+    <t>PREFEITURA SP- ISS</t>
+  </si>
+  <si>
     <t>Roger Duarte Pinheiro Me</t>
   </si>
   <si>
-    <t>PREFEITURA SP- ISS</t>
-  </si>
-  <si>
     <t>12/12/2026</t>
   </si>
   <si>
@@ -264,15 +285,6 @@
     <t>GABRIEL DE CARVALHO MELLO</t>
   </si>
   <si>
-    <t>16/12/2026</t>
-  </si>
-  <si>
-    <t>105101 - 2</t>
-  </si>
-  <si>
-    <t>Claudio Wasserman</t>
-  </si>
-  <si>
     <t>18/12/2026</t>
   </si>
   <si>
@@ -300,18 +312,18 @@
     <t>20/12/2026</t>
   </si>
   <si>
+    <t>Simples Nacional - DAS</t>
+  </si>
+  <si>
     <t>IRRF- darf</t>
   </si>
   <si>
-    <t>Simples Nacional - DAS</t>
+    <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
   </si>
   <si>
     <t>INSS- Previdenciária</t>
   </si>
   <si>
-    <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
-  </si>
-  <si>
     <t>22/12/2026</t>
   </si>
   <si>
@@ -348,19 +360,19 @@
     <t>Total Geral Crédito</t>
   </si>
   <si>
-    <t>20.261,53</t>
+    <t>10.081,53</t>
   </si>
   <si>
     <t>Total Geral Débito</t>
   </si>
   <si>
-    <t>102.445,57</t>
+    <t>104.990,61</t>
   </si>
   <si>
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-82.184,04</t>
+    <t>-94.909,08</t>
   </si>
 </sst>
 </file>
@@ -428,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H76"/>
+  <dimension ref="A2:H79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -668,19 +680,19 @@
         <v>28</v>
       </c>
       <c r="D23" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="E23" t="s" s="1">
         <v>37</v>
       </c>
-      <c r="E23" t="s" s="1">
-        <v>38</v>
-      </c>
       <c r="F23" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G23" t="n" s="1">
-        <v>14250.0</v>
+        <v>2536.0</v>
       </c>
       <c r="H23" t="n" s="1">
-        <v>-14250.0</v>
+        <v>-2536.0</v>
       </c>
     </row>
     <row r="24">
@@ -694,7 +706,7 @@
         <v>28</v>
       </c>
       <c r="D24" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E24" t="s" s="1">
         <v>39</v>
@@ -703,10 +715,10 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n" s="1">
-        <v>2536.0</v>
+        <v>2219.85</v>
       </c>
       <c r="H24" t="n" s="1">
-        <v>-2536.0</v>
+        <v>-2219.85</v>
       </c>
     </row>
     <row r="25">
@@ -720,19 +732,19 @@
         <v>28</v>
       </c>
       <c r="D25" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="E25" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="E25" t="s" s="1">
-        <v>41</v>
-      </c>
       <c r="F25" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G25" t="n" s="1">
-        <v>2219.85</v>
+        <v>9.99</v>
       </c>
       <c r="H25" t="n" s="1">
-        <v>-2219.85</v>
+        <v>-9.99</v>
       </c>
     </row>
     <row r="26">
@@ -749,16 +761,16 @@
         <v>35</v>
       </c>
       <c r="E26" t="s" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F26" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G26" t="n" s="1">
-        <v>9.99</v>
+        <v>1000.0</v>
       </c>
       <c r="H26" t="n" s="1">
-        <v>-9.99</v>
+        <v>-1000.0</v>
       </c>
     </row>
     <row r="27">
@@ -772,7 +784,7 @@
         <v>28</v>
       </c>
       <c r="D27" t="s" s="1">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E27" t="s" s="1">
         <v>43</v>
@@ -781,10 +793,10 @@
         <v>0.0</v>
       </c>
       <c r="G27" t="n" s="1">
-        <v>1000.0</v>
+        <v>14250.0</v>
       </c>
       <c r="H27" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-14250.0</v>
       </c>
     </row>
     <row r="28">
@@ -833,10 +845,10 @@
         <v>0.0</v>
       </c>
       <c r="G29" t="n" s="1">
-        <v>49.95</v>
+        <v>4020.07</v>
       </c>
       <c r="H29" t="n" s="1">
-        <v>-49.95</v>
+        <v>-4020.07</v>
       </c>
     </row>
     <row r="30">
@@ -1041,10 +1053,10 @@
         <v>0.0</v>
       </c>
       <c r="G37" t="n" s="1">
-        <v>4020.07</v>
+        <v>150.0</v>
       </c>
       <c r="H37" t="n" s="1">
-        <v>-4020.07</v>
+        <v>-150.0</v>
       </c>
     </row>
     <row r="38">
@@ -1067,10 +1079,10 @@
         <v>0.0</v>
       </c>
       <c r="G38" t="n" s="1">
-        <v>150.0</v>
+        <v>1900.0</v>
       </c>
       <c r="H38" t="n" s="1">
-        <v>-150.0</v>
+        <v>-1900.0</v>
       </c>
     </row>
     <row r="39">
@@ -1093,10 +1105,10 @@
         <v>0.0</v>
       </c>
       <c r="G39" t="n" s="1">
-        <v>1900.0</v>
+        <v>49.95</v>
       </c>
       <c r="H39" t="n" s="1">
-        <v>-1900.0</v>
+        <v>-49.95</v>
       </c>
     </row>
     <row r="40">
@@ -1119,10 +1131,10 @@
         <v>0.0</v>
       </c>
       <c r="G40" t="n" s="1">
-        <v>160.0</v>
+        <v>6000.0</v>
       </c>
       <c r="H40" t="n" s="1">
-        <v>-160.0</v>
+        <v>-6000.0</v>
       </c>
     </row>
     <row r="41">
@@ -1145,10 +1157,10 @@
         <v>0.0</v>
       </c>
       <c r="G41" t="n" s="1">
-        <v>1800.0</v>
+        <v>2479.65</v>
       </c>
       <c r="H41" t="n" s="1">
-        <v>-1800.0</v>
+        <v>-2479.65</v>
       </c>
     </row>
     <row r="42">
@@ -1171,10 +1183,10 @@
         <v>0.0</v>
       </c>
       <c r="G42" t="n" s="1">
-        <v>2479.65</v>
+        <v>1800.0</v>
       </c>
       <c r="H42" t="n" s="1">
-        <v>-2479.65</v>
+        <v>-1800.0</v>
       </c>
     </row>
     <row r="43">
@@ -1197,10 +1209,10 @@
         <v>0.0</v>
       </c>
       <c r="G43" t="n" s="1">
-        <v>6000.0</v>
+        <v>160.0</v>
       </c>
       <c r="H43" t="n" s="1">
-        <v>-6000.0</v>
+        <v>-160.0</v>
       </c>
     </row>
     <row r="44">
@@ -1416,25 +1428,25 @@
         <v>26</v>
       </c>
       <c r="B52" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="C52" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D52" t="s" s="1">
         <v>72</v>
       </c>
-      <c r="C52" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D52" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E52" t="s" s="1">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="F52" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G52" t="n" s="1">
-        <v>599.0</v>
+        <v>85.91</v>
       </c>
       <c r="H52" t="n" s="1">
-        <v>-599.0</v>
+        <v>-85.91</v>
       </c>
     </row>
     <row r="53">
@@ -1442,25 +1454,25 @@
         <v>26</v>
       </c>
       <c r="B53" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="C53" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D53" t="s" s="1">
+        <v>74</v>
+      </c>
+      <c r="E53" t="s" s="1">
         <v>73</v>
       </c>
-      <c r="C53" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D53" t="s" s="1">
-        <v>37</v>
-      </c>
-      <c r="E53" t="s" s="1">
-        <v>74</v>
-      </c>
       <c r="F53" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G53" t="n" s="1">
-        <v>968.0</v>
+        <v>131.13</v>
       </c>
       <c r="H53" t="n" s="1">
-        <v>-968.0</v>
+        <v>-131.13</v>
       </c>
     </row>
     <row r="54">
@@ -1468,25 +1480,25 @@
         <v>26</v>
       </c>
       <c r="B54" t="s" s="1">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="C54" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D54" t="s" s="1">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="E54" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F54" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G54" t="n" s="1">
-        <v>4.16</v>
+        <v>1060.0</v>
       </c>
       <c r="H54" t="n" s="1">
-        <v>-4.16</v>
+        <v>-1060.0</v>
       </c>
     </row>
     <row r="55">
@@ -1494,7 +1506,7 @@
         <v>26</v>
       </c>
       <c r="B55" t="s" s="1">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="C55" t="s" s="1">
         <v>28</v>
@@ -1509,10 +1521,10 @@
         <v>0.0</v>
       </c>
       <c r="G55" t="n" s="1">
-        <v>750.0</v>
+        <v>1268.0</v>
       </c>
       <c r="H55" t="n" s="1">
-        <v>-750.0</v>
+        <v>-1268.0</v>
       </c>
     </row>
     <row r="56">
@@ -1523,22 +1535,22 @@
         <v>79</v>
       </c>
       <c r="C56" t="s" s="1">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="D56" t="s" s="1">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="E56" t="s" s="1">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="F56" t="n" s="1">
-        <v>1816.53</v>
+        <v>0.0</v>
       </c>
       <c r="G56" t="n" s="1">
-        <v>0.0</v>
+        <v>599.0</v>
       </c>
       <c r="H56" t="n" s="1">
-        <v>1816.53</v>
+        <v>-599.0</v>
       </c>
     </row>
     <row r="57">
@@ -1546,25 +1558,25 @@
         <v>26</v>
       </c>
       <c r="B57" t="s" s="1">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C57" t="s" s="1">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="D57" t="s" s="1">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="E57" t="s" s="1">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F57" t="n" s="1">
-        <v>10180.0</v>
+        <v>0.0</v>
       </c>
       <c r="G57" t="n" s="1">
-        <v>0.0</v>
+        <v>4.16</v>
       </c>
       <c r="H57" t="n" s="1">
-        <v>10180.0</v>
+        <v>-4.16</v>
       </c>
     </row>
     <row r="58">
@@ -1572,25 +1584,25 @@
         <v>26</v>
       </c>
       <c r="B58" t="s" s="1">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C58" t="s" s="1">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="D58" t="s" s="1">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="E58" t="s" s="1">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F58" t="n" s="1">
-        <v>7425.0</v>
+        <v>0.0</v>
       </c>
       <c r="G58" t="n" s="1">
-        <v>0.0</v>
+        <v>968.0</v>
       </c>
       <c r="H58" t="n" s="1">
-        <v>7425.0</v>
+        <v>-968.0</v>
       </c>
     </row>
     <row r="59">
@@ -1598,25 +1610,25 @@
         <v>26</v>
       </c>
       <c r="B59" t="s" s="1">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C59" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D59" t="s" s="1">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="E59" t="s" s="1">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F59" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G59" t="n" s="1">
-        <v>4588.5</v>
+        <v>750.0</v>
       </c>
       <c r="H59" t="n" s="1">
-        <v>-4588.5</v>
+        <v>-750.0</v>
       </c>
     </row>
     <row r="60">
@@ -1627,22 +1639,22 @@
         <v>86</v>
       </c>
       <c r="C60" t="s" s="1">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="D60" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E60" t="s" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F60" t="n" s="1">
-        <v>0.0</v>
+        <v>1816.53</v>
       </c>
       <c r="G60" t="n" s="1">
-        <v>239.58</v>
+        <v>0.0</v>
       </c>
       <c r="H60" t="n" s="1">
-        <v>-239.58</v>
+        <v>1816.53</v>
       </c>
     </row>
     <row r="61">
@@ -1650,25 +1662,25 @@
         <v>26</v>
       </c>
       <c r="B61" t="s" s="1">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C61" t="s" s="1">
+        <v>87</v>
+      </c>
+      <c r="D61" t="s" s="1">
+        <v>91</v>
+      </c>
+      <c r="E61" t="s" s="1">
         <v>92</v>
       </c>
-      <c r="D61" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="E61" t="s" s="1">
-        <v>93</v>
-      </c>
       <c r="F61" t="n" s="1">
-        <v>840.0</v>
+        <v>7425.0</v>
       </c>
       <c r="G61" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="H61" t="n" s="1">
-        <v>840.0</v>
+        <v>7425.0</v>
       </c>
     </row>
     <row r="62">
@@ -1676,25 +1688,25 @@
         <v>26</v>
       </c>
       <c r="B62" t="s" s="1">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C62" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D62" t="s" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E62" t="s" s="1">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F62" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G62" t="n" s="1">
-        <v>4500.0</v>
+        <v>4588.5</v>
       </c>
       <c r="H62" t="n" s="1">
-        <v>-4500.0</v>
+        <v>-4588.5</v>
       </c>
     </row>
     <row r="63">
@@ -1702,25 +1714,25 @@
         <v>26</v>
       </c>
       <c r="B63" t="s" s="1">
+        <v>90</v>
+      </c>
+      <c r="C63" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D63" t="s" s="1">
         <v>94</v>
       </c>
-      <c r="C63" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D63" t="s" s="1">
-        <v>37</v>
-      </c>
       <c r="E63" t="s" s="1">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F63" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G63" t="n" s="1">
-        <v>15000.0</v>
+        <v>239.58</v>
       </c>
       <c r="H63" t="n" s="1">
-        <v>-15000.0</v>
+        <v>-239.58</v>
       </c>
     </row>
     <row r="64">
@@ -1728,25 +1740,25 @@
         <v>26</v>
       </c>
       <c r="B64" t="s" s="1">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C64" t="s" s="1">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E64" t="s" s="1">
         <v>97</v>
       </c>
       <c r="F64" t="n" s="1">
-        <v>0.0</v>
+        <v>840.0</v>
       </c>
       <c r="G64" t="n" s="1">
-        <v>1500.0</v>
+        <v>0.0</v>
       </c>
       <c r="H64" t="n" s="1">
-        <v>-1500.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="65">
@@ -1754,25 +1766,25 @@
         <v>26</v>
       </c>
       <c r="B65" t="s" s="1">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C65" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D65" t="s" s="1">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E65" t="s" s="1">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F65" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G65" t="n" s="1">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="H65" t="n" s="1">
-        <v>-2000.0</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="66">
@@ -1780,25 +1792,25 @@
         <v>26</v>
       </c>
       <c r="B66" t="s" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C66" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D66" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E66" t="s" s="1">
         <v>100</v>
       </c>
-      <c r="E66" t="s" s="1">
-        <v>101</v>
-      </c>
       <c r="F66" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G66" t="n" s="1">
-        <v>146.67</v>
+        <v>4500.0</v>
       </c>
       <c r="H66" t="n" s="1">
-        <v>-146.67</v>
+        <v>-4500.0</v>
       </c>
     </row>
     <row r="67">
@@ -1806,25 +1818,25 @@
         <v>26</v>
       </c>
       <c r="B67" t="s" s="1">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C67" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D67" t="s" s="1">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="E67" t="s" s="1">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="F67" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G67" t="n" s="1">
-        <v>180.06</v>
+        <v>2000.0</v>
       </c>
       <c r="H67" t="n" s="1">
-        <v>-180.06</v>
+        <v>-2000.0</v>
       </c>
     </row>
     <row r="68">
@@ -1832,25 +1844,25 @@
         <v>26</v>
       </c>
       <c r="B68" t="s" s="1">
+        <v>98</v>
+      </c>
+      <c r="C68" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D68" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E68" t="s" s="1">
         <v>102</v>
       </c>
-      <c r="C68" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D68" t="s" s="1">
-        <v>103</v>
-      </c>
-      <c r="E68" t="s" s="1">
-        <v>104</v>
-      </c>
       <c r="F68" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G68" t="n" s="1">
-        <v>1925.0</v>
+        <v>1500.0</v>
       </c>
       <c r="H68" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-1500.0</v>
       </c>
     </row>
     <row r="69">
@@ -1858,25 +1870,25 @@
         <v>26</v>
       </c>
       <c r="B69" t="s" s="1">
+        <v>103</v>
+      </c>
+      <c r="C69" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D69" t="s" s="1">
+        <v>104</v>
+      </c>
+      <c r="E69" t="s" s="1">
         <v>105</v>
       </c>
-      <c r="C69" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D69" t="s" s="1">
-        <v>77</v>
-      </c>
-      <c r="E69" t="s" s="1">
-        <v>106</v>
-      </c>
       <c r="F69" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G69" t="n" s="1">
-        <v>1201.89</v>
+        <v>146.67</v>
       </c>
       <c r="H69" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-146.67</v>
       </c>
     </row>
     <row r="70">
@@ -1884,25 +1896,25 @@
         <v>26</v>
       </c>
       <c r="B70" t="s" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C70" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D70" t="s" s="1">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="E70" t="s" s="1">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="F70" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G70" t="n" s="1">
-        <v>1000.0</v>
+        <v>180.06</v>
       </c>
       <c r="H70" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-180.06</v>
       </c>
     </row>
     <row r="71">
@@ -1910,49 +1922,127 @@
         <v>26</v>
       </c>
       <c r="B71" t="s" s="1">
+        <v>106</v>
+      </c>
+      <c r="C71" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D71" t="s" s="1">
         <v>107</v>
       </c>
-      <c r="C71" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D71" t="s" s="1">
-        <v>37</v>
-      </c>
       <c r="E71" t="s" s="1">
+        <v>108</v>
+      </c>
+      <c r="F71" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G71" t="n" s="1">
+        <v>1925.0</v>
+      </c>
+      <c r="H71" t="n" s="1">
+        <v>-1925.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B72" t="s" s="1">
         <v>109</v>
       </c>
-      <c r="F71" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G71" t="n" s="1">
+      <c r="C72" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D72" t="s" s="1">
+        <v>84</v>
+      </c>
+      <c r="E72" t="s" s="1">
+        <v>110</v>
+      </c>
+      <c r="F72" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G72" t="n" s="1">
+        <v>1201.89</v>
+      </c>
+      <c r="H72" t="n" s="1">
+        <v>-1201.89</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B73" t="s" s="1">
+        <v>111</v>
+      </c>
+      <c r="C73" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D73" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="E73" t="s" s="1">
+        <v>112</v>
+      </c>
+      <c r="F73" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G73" t="n" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="H73" t="n" s="1">
+        <v>-1000.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B74" t="s" s="1">
+        <v>111</v>
+      </c>
+      <c r="C74" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D74" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E74" t="s" s="1">
+        <v>113</v>
+      </c>
+      <c r="F74" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G74" t="n" s="1">
         <v>3750.0</v>
       </c>
-      <c r="H71" t="n" s="1">
+      <c r="H74" t="n" s="1">
         <v>-3750.0</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="s">
+    <row r="77">
+      <c r="A77" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B77" s="3" t="s">
         <v>115</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="122">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -153,30 +153,30 @@
     <t>Promob</t>
   </si>
   <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>FERNANDO OLIVEIRA LEITE</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>SINDICATO DO COM VAREJ E LOJISTA DO COM DE SP - SI</t>
+  </si>
+  <si>
+    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
+  </si>
+  <si>
     <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>FERNANDO OLIVEIRA LEITE</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>SINDICATO DO COM VAREJ E LOJISTA DO COM DE SP - SI</t>
-  </si>
-  <si>
-    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
     <t>Jackson Fernando de Araujo</t>
   </si>
   <si>
@@ -252,18 +252,24 @@
     <t>RAYSSA BARBOSA SILVA</t>
   </si>
   <si>
+    <t>80 - 2</t>
+  </si>
+  <si>
+    <t>Mayara Silva Martins</t>
+  </si>
+  <si>
     <t>08/12/2026</t>
   </si>
   <si>
     <t>10/12/2026</t>
   </si>
   <si>
+    <t>Roger Duarte Pinheiro Me</t>
+  </si>
+  <si>
     <t>PREFEITURA SP- ISS</t>
   </si>
   <si>
-    <t>Roger Duarte Pinheiro Me</t>
-  </si>
-  <si>
     <t>12/12/2026</t>
   </si>
   <si>
@@ -366,13 +372,13 @@
     <t>Total Geral Débito</t>
   </si>
   <si>
-    <t>104.990,61</t>
+    <t>106.306,21</t>
   </si>
   <si>
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-94.909,08</t>
+    <t>-96.224,68</t>
   </si>
 </sst>
 </file>
@@ -440,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H79"/>
+  <dimension ref="A2:H80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -845,10 +851,10 @@
         <v>0.0</v>
       </c>
       <c r="G29" t="n" s="1">
-        <v>4020.07</v>
+        <v>1000.0</v>
       </c>
       <c r="H29" t="n" s="1">
-        <v>-4020.07</v>
+        <v>-1000.0</v>
       </c>
     </row>
     <row r="30">
@@ -1027,10 +1033,10 @@
         <v>0.0</v>
       </c>
       <c r="G36" t="n" s="1">
-        <v>1000.0</v>
+        <v>4020.07</v>
       </c>
       <c r="H36" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-4020.07</v>
       </c>
     </row>
     <row r="37">
@@ -1532,25 +1538,25 @@
         <v>26</v>
       </c>
       <c r="B56" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="C56" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D56" t="s" s="1">
         <v>79</v>
       </c>
-      <c r="C56" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D56" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E56" t="s" s="1">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="F56" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G56" t="n" s="1">
-        <v>599.0</v>
+        <v>1315.6</v>
       </c>
       <c r="H56" t="n" s="1">
-        <v>-599.0</v>
+        <v>-1315.6</v>
       </c>
     </row>
     <row r="57">
@@ -1558,25 +1564,25 @@
         <v>26</v>
       </c>
       <c r="B57" t="s" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C57" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D57" t="s" s="1">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E57" t="s" s="1">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="F57" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G57" t="n" s="1">
-        <v>4.16</v>
+        <v>599.0</v>
       </c>
       <c r="H57" t="n" s="1">
-        <v>-4.16</v>
+        <v>-599.0</v>
       </c>
     </row>
     <row r="58">
@@ -1584,7 +1590,7 @@
         <v>26</v>
       </c>
       <c r="B58" t="s" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C58" t="s" s="1">
         <v>28</v>
@@ -1593,7 +1599,7 @@
         <v>42</v>
       </c>
       <c r="E58" t="s" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F58" t="n" s="1">
         <v>0.0</v>
@@ -1610,25 +1616,25 @@
         <v>26</v>
       </c>
       <c r="B59" t="s" s="1">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C59" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D59" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E59" t="s" s="1">
         <v>84</v>
       </c>
-      <c r="E59" t="s" s="1">
-        <v>85</v>
-      </c>
       <c r="F59" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G59" t="n" s="1">
-        <v>750.0</v>
+        <v>4.16</v>
       </c>
       <c r="H59" t="n" s="1">
-        <v>-750.0</v>
+        <v>-4.16</v>
       </c>
     </row>
     <row r="60">
@@ -1636,25 +1642,25 @@
         <v>26</v>
       </c>
       <c r="B60" t="s" s="1">
+        <v>85</v>
+      </c>
+      <c r="C60" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D60" t="s" s="1">
         <v>86</v>
       </c>
-      <c r="C60" t="s" s="1">
+      <c r="E60" t="s" s="1">
         <v>87</v>
       </c>
-      <c r="D60" t="s" s="1">
-        <v>88</v>
-      </c>
-      <c r="E60" t="s" s="1">
-        <v>89</v>
-      </c>
       <c r="F60" t="n" s="1">
-        <v>1816.53</v>
+        <v>0.0</v>
       </c>
       <c r="G60" t="n" s="1">
-        <v>0.0</v>
+        <v>750.0</v>
       </c>
       <c r="H60" t="n" s="1">
-        <v>1816.53</v>
+        <v>-750.0</v>
       </c>
     </row>
     <row r="61">
@@ -1662,25 +1668,25 @@
         <v>26</v>
       </c>
       <c r="B61" t="s" s="1">
+        <v>88</v>
+      </c>
+      <c r="C61" t="s" s="1">
+        <v>89</v>
+      </c>
+      <c r="D61" t="s" s="1">
         <v>90</v>
       </c>
-      <c r="C61" t="s" s="1">
-        <v>87</v>
-      </c>
-      <c r="D61" t="s" s="1">
+      <c r="E61" t="s" s="1">
         <v>91</v>
       </c>
-      <c r="E61" t="s" s="1">
-        <v>92</v>
-      </c>
       <c r="F61" t="n" s="1">
-        <v>7425.0</v>
+        <v>1816.53</v>
       </c>
       <c r="G61" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="H61" t="n" s="1">
-        <v>7425.0</v>
+        <v>1816.53</v>
       </c>
     </row>
     <row r="62">
@@ -1688,25 +1694,25 @@
         <v>26</v>
       </c>
       <c r="B62" t="s" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C62" t="s" s="1">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="D62" t="s" s="1">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="E62" t="s" s="1">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F62" t="n" s="1">
-        <v>0.0</v>
+        <v>7425.0</v>
       </c>
       <c r="G62" t="n" s="1">
-        <v>4588.5</v>
+        <v>0.0</v>
       </c>
       <c r="H62" t="n" s="1">
-        <v>-4588.5</v>
+        <v>7425.0</v>
       </c>
     </row>
     <row r="63">
@@ -1714,13 +1720,13 @@
         <v>26</v>
       </c>
       <c r="B63" t="s" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C63" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D63" t="s" s="1">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="E63" t="s" s="1">
         <v>95</v>
@@ -1729,10 +1735,10 @@
         <v>0.0</v>
       </c>
       <c r="G63" t="n" s="1">
-        <v>239.58</v>
+        <v>4588.5</v>
       </c>
       <c r="H63" t="n" s="1">
-        <v>-239.58</v>
+        <v>-4588.5</v>
       </c>
     </row>
     <row r="64">
@@ -1740,25 +1746,25 @@
         <v>26</v>
       </c>
       <c r="B64" t="s" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D64" t="s" s="1">
         <v>96</v>
-      </c>
-      <c r="D64" t="s" s="1">
-        <v>35</v>
       </c>
       <c r="E64" t="s" s="1">
         <v>97</v>
       </c>
       <c r="F64" t="n" s="1">
-        <v>840.0</v>
+        <v>0.0</v>
       </c>
       <c r="G64" t="n" s="1">
-        <v>0.0</v>
+        <v>239.58</v>
       </c>
       <c r="H64" t="n" s="1">
-        <v>840.0</v>
+        <v>-239.58</v>
       </c>
     </row>
     <row r="65">
@@ -1766,25 +1772,25 @@
         <v>26</v>
       </c>
       <c r="B65" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C65" t="s" s="1">
         <v>98</v>
       </c>
-      <c r="C65" t="s" s="1">
-        <v>28</v>
-      </c>
       <c r="D65" t="s" s="1">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E65" t="s" s="1">
         <v>99</v>
       </c>
       <c r="F65" t="n" s="1">
-        <v>0.0</v>
+        <v>840.0</v>
       </c>
       <c r="G65" t="n" s="1">
-        <v>15000.0</v>
+        <v>0.0</v>
       </c>
       <c r="H65" t="n" s="1">
-        <v>-15000.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="66">
@@ -1792,7 +1798,7 @@
         <v>26</v>
       </c>
       <c r="B66" t="s" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C66" t="s" s="1">
         <v>28</v>
@@ -1801,16 +1807,16 @@
         <v>42</v>
       </c>
       <c r="E66" t="s" s="1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F66" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G66" t="n" s="1">
-        <v>4500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="H66" t="n" s="1">
-        <v>-4500.0</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="67">
@@ -1818,7 +1824,7 @@
         <v>26</v>
       </c>
       <c r="B67" t="s" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C67" t="s" s="1">
         <v>28</v>
@@ -1827,16 +1833,16 @@
         <v>42</v>
       </c>
       <c r="E67" t="s" s="1">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F67" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G67" t="n" s="1">
-        <v>2000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="H67" t="n" s="1">
-        <v>-2000.0</v>
+        <v>-4500.0</v>
       </c>
     </row>
     <row r="68">
@@ -1844,7 +1850,7 @@
         <v>26</v>
       </c>
       <c r="B68" t="s" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C68" t="s" s="1">
         <v>28</v>
@@ -1853,16 +1859,16 @@
         <v>42</v>
       </c>
       <c r="E68" t="s" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F68" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G68" t="n" s="1">
-        <v>1500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="H68" t="n" s="1">
-        <v>-1500.0</v>
+        <v>-2000.0</v>
       </c>
     </row>
     <row r="69">
@@ -1870,25 +1876,25 @@
         <v>26</v>
       </c>
       <c r="B69" t="s" s="1">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C69" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D69" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E69" t="s" s="1">
         <v>104</v>
       </c>
-      <c r="E69" t="s" s="1">
-        <v>105</v>
-      </c>
       <c r="F69" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G69" t="n" s="1">
-        <v>146.67</v>
+        <v>1500.0</v>
       </c>
       <c r="H69" t="n" s="1">
-        <v>-146.67</v>
+        <v>-1500.0</v>
       </c>
     </row>
     <row r="70">
@@ -1896,25 +1902,25 @@
         <v>26</v>
       </c>
       <c r="B70" t="s" s="1">
+        <v>105</v>
+      </c>
+      <c r="C70" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D70" t="s" s="1">
         <v>106</v>
       </c>
-      <c r="C70" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D70" t="s" s="1">
-        <v>84</v>
-      </c>
       <c r="E70" t="s" s="1">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="F70" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G70" t="n" s="1">
-        <v>180.06</v>
+        <v>146.67</v>
       </c>
       <c r="H70" t="n" s="1">
-        <v>-180.06</v>
+        <v>-146.67</v>
       </c>
     </row>
     <row r="71">
@@ -1922,25 +1928,25 @@
         <v>26</v>
       </c>
       <c r="B71" t="s" s="1">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C71" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D71" t="s" s="1">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="E71" t="s" s="1">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="F71" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G71" t="n" s="1">
-        <v>1925.0</v>
+        <v>180.06</v>
       </c>
       <c r="H71" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-180.06</v>
       </c>
     </row>
     <row r="72">
@@ -1948,13 +1954,13 @@
         <v>26</v>
       </c>
       <c r="B72" t="s" s="1">
+        <v>108</v>
+      </c>
+      <c r="C72" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D72" t="s" s="1">
         <v>109</v>
-      </c>
-      <c r="C72" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D72" t="s" s="1">
-        <v>84</v>
       </c>
       <c r="E72" t="s" s="1">
         <v>110</v>
@@ -1963,10 +1969,10 @@
         <v>0.0</v>
       </c>
       <c r="G72" t="n" s="1">
-        <v>1201.89</v>
+        <v>1925.0</v>
       </c>
       <c r="H72" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="73">
@@ -1980,7 +1986,7 @@
         <v>28</v>
       </c>
       <c r="D73" t="s" s="1">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="E73" t="s" s="1">
         <v>112</v>
@@ -1989,10 +1995,10 @@
         <v>0.0</v>
       </c>
       <c r="G73" t="n" s="1">
-        <v>1000.0</v>
+        <v>1201.89</v>
       </c>
       <c r="H73" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-1201.89</v>
       </c>
     </row>
     <row r="74">
@@ -2000,33 +2006,51 @@
         <v>26</v>
       </c>
       <c r="B74" t="s" s="1">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C74" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D74" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="E74" t="s" s="1">
+        <v>114</v>
+      </c>
+      <c r="F74" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G74" t="n" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="H74" t="n" s="1">
+        <v>-1000.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B75" t="s" s="1">
+        <v>113</v>
+      </c>
+      <c r="C75" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D75" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="E74" t="s" s="1">
-        <v>113</v>
-      </c>
-      <c r="F74" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G74" t="n" s="1">
+      <c r="E75" t="s" s="1">
+        <v>115</v>
+      </c>
+      <c r="F75" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G75" t="n" s="1">
         <v>3750.0</v>
       </c>
-      <c r="H74" t="n" s="1">
+      <c r="H75" t="n" s="1">
         <v>-3750.0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="78">
@@ -2043,6 +2067,14 @@
       </c>
       <c r="B79" s="3" t="s">
         <v>119</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="125">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -126,6 +126,12 @@
     <t>Eric Kevin de Souza Serpa</t>
   </si>
   <si>
+    <t>1 - 11</t>
+  </si>
+  <si>
+    <t>DECORA INTERIORES LTDA</t>
+  </si>
+  <si>
     <t>bianca rodrigues</t>
   </si>
   <si>
@@ -141,42 +147,36 @@
     <t>FERNANDA DOCHVAT SILVA</t>
   </si>
   <si>
-    <t>1 - 11</t>
-  </si>
-  <si>
-    <t>DECORA INTERIORES LTDA</t>
-  </si>
-  <si>
     <t>3 - 10</t>
   </si>
   <si>
     <t>Promob</t>
   </si>
   <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>FERNANDO OLIVEIRA LEITE</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>SINDICATO DO COM VAREJ E LOJISTA DO COM DE SP - SI</t>
+  </si>
+  <si>
+    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
+  </si>
+  <si>
     <t>Teresinha Elvira Maximino de Menezes</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>FERNANDO OLIVEIRA LEITE</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>SINDICATO DO COM VAREJ E LOJISTA DO COM DE SP - SI</t>
-  </si>
-  <si>
-    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
     <t>Jackson Fernando de Araujo</t>
   </si>
   <si>
@@ -318,18 +318,18 @@
     <t>20/12/2026</t>
   </si>
   <si>
+    <t>INSS- Previdenciária</t>
+  </si>
+  <si>
+    <t>IRRF- darf</t>
+  </si>
+  <si>
     <t>Simples Nacional - DAS</t>
   </si>
   <si>
-    <t>IRRF- darf</t>
-  </si>
-  <si>
     <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
   </si>
   <si>
-    <t>INSS- Previdenciária</t>
-  </si>
-  <si>
     <t>22/12/2026</t>
   </si>
   <si>
@@ -339,6 +339,15 @@
     <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
   </si>
   <si>
+    <t>23/12/2026</t>
+  </si>
+  <si>
+    <t>105501 - 2</t>
+  </si>
+  <si>
+    <t>Willian Rodrigues Lima</t>
+  </si>
+  <si>
     <t>25/12/2026</t>
   </si>
   <si>
@@ -366,7 +375,7 @@
     <t>Total Geral Crédito</t>
   </si>
   <si>
-    <t>10.081,53</t>
+    <t>11.342,40</t>
   </si>
   <si>
     <t>Total Geral Débito</t>
@@ -378,7 +387,7 @@
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-96.224,68</t>
+    <t>-94.963,81</t>
   </si>
 </sst>
 </file>
@@ -446,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H80"/>
+  <dimension ref="A2:H81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -686,19 +695,19 @@
         <v>28</v>
       </c>
       <c r="D23" t="s" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E23" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F23" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G23" t="n" s="1">
-        <v>2536.0</v>
+        <v>14250.0</v>
       </c>
       <c r="H23" t="n" s="1">
-        <v>-2536.0</v>
+        <v>-14250.0</v>
       </c>
     </row>
     <row r="24">
@@ -712,7 +721,7 @@
         <v>28</v>
       </c>
       <c r="D24" t="s" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s" s="1">
         <v>39</v>
@@ -721,10 +730,10 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n" s="1">
-        <v>2219.85</v>
+        <v>2536.0</v>
       </c>
       <c r="H24" t="n" s="1">
-        <v>-2219.85</v>
+        <v>-2536.0</v>
       </c>
     </row>
     <row r="25">
@@ -738,19 +747,19 @@
         <v>28</v>
       </c>
       <c r="D25" t="s" s="1">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E25" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F25" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G25" t="n" s="1">
-        <v>9.99</v>
+        <v>2219.85</v>
       </c>
       <c r="H25" t="n" s="1">
-        <v>-9.99</v>
+        <v>-2219.85</v>
       </c>
     </row>
     <row r="26">
@@ -767,16 +776,16 @@
         <v>35</v>
       </c>
       <c r="E26" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F26" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G26" t="n" s="1">
-        <v>1000.0</v>
+        <v>9.99</v>
       </c>
       <c r="H26" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-9.99</v>
       </c>
     </row>
     <row r="27">
@@ -790,7 +799,7 @@
         <v>28</v>
       </c>
       <c r="D27" t="s" s="1">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E27" t="s" s="1">
         <v>43</v>
@@ -799,10 +808,10 @@
         <v>0.0</v>
       </c>
       <c r="G27" t="n" s="1">
-        <v>14250.0</v>
+        <v>1000.0</v>
       </c>
       <c r="H27" t="n" s="1">
-        <v>-14250.0</v>
+        <v>-1000.0</v>
       </c>
     </row>
     <row r="28">
@@ -851,10 +860,10 @@
         <v>0.0</v>
       </c>
       <c r="G29" t="n" s="1">
-        <v>1000.0</v>
+        <v>4020.07</v>
       </c>
       <c r="H29" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-4020.07</v>
       </c>
     </row>
     <row r="30">
@@ -1033,10 +1042,10 @@
         <v>0.0</v>
       </c>
       <c r="G36" t="n" s="1">
-        <v>4020.07</v>
+        <v>1000.0</v>
       </c>
       <c r="H36" t="n" s="1">
-        <v>-4020.07</v>
+        <v>-1000.0</v>
       </c>
     </row>
     <row r="37">
@@ -1596,7 +1605,7 @@
         <v>28</v>
       </c>
       <c r="D58" t="s" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E58" t="s" s="1">
         <v>83</v>
@@ -1622,7 +1631,7 @@
         <v>28</v>
       </c>
       <c r="D59" t="s" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E59" t="s" s="1">
         <v>84</v>
@@ -1804,7 +1813,7 @@
         <v>28</v>
       </c>
       <c r="D66" t="s" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E66" t="s" s="1">
         <v>101</v>
@@ -1813,10 +1822,10 @@
         <v>0.0</v>
       </c>
       <c r="G66" t="n" s="1">
-        <v>15000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="H66" t="n" s="1">
-        <v>-15000.0</v>
+        <v>-1500.0</v>
       </c>
     </row>
     <row r="67">
@@ -1830,7 +1839,7 @@
         <v>28</v>
       </c>
       <c r="D67" t="s" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E67" t="s" s="1">
         <v>102</v>
@@ -1856,7 +1865,7 @@
         <v>28</v>
       </c>
       <c r="D68" t="s" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E68" t="s" s="1">
         <v>103</v>
@@ -1865,10 +1874,10 @@
         <v>0.0</v>
       </c>
       <c r="G68" t="n" s="1">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="H68" t="n" s="1">
-        <v>-2000.0</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="69">
@@ -1882,7 +1891,7 @@
         <v>28</v>
       </c>
       <c r="D69" t="s" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E69" t="s" s="1">
         <v>104</v>
@@ -1891,10 +1900,10 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n" s="1">
-        <v>1500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="H69" t="n" s="1">
-        <v>-1500.0</v>
+        <v>-2000.0</v>
       </c>
     </row>
     <row r="70">
@@ -1931,22 +1940,22 @@
         <v>108</v>
       </c>
       <c r="C71" t="s" s="1">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="D71" t="s" s="1">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="E71" t="s" s="1">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="F71" t="n" s="1">
-        <v>0.0</v>
+        <v>1260.87</v>
       </c>
       <c r="G71" t="n" s="1">
-        <v>180.06</v>
+        <v>0.0</v>
       </c>
       <c r="H71" t="n" s="1">
-        <v>-180.06</v>
+        <v>1260.87</v>
       </c>
     </row>
     <row r="72">
@@ -1954,25 +1963,25 @@
         <v>26</v>
       </c>
       <c r="B72" t="s" s="1">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C72" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D72" t="s" s="1">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="E72" t="s" s="1">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="F72" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G72" t="n" s="1">
-        <v>1925.0</v>
+        <v>180.06</v>
       </c>
       <c r="H72" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-180.06</v>
       </c>
     </row>
     <row r="73">
@@ -1986,19 +1995,19 @@
         <v>28</v>
       </c>
       <c r="D73" t="s" s="1">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="E73" t="s" s="1">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F73" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G73" t="n" s="1">
-        <v>1201.89</v>
+        <v>1925.0</v>
       </c>
       <c r="H73" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="74">
@@ -2006,25 +2015,25 @@
         <v>26</v>
       </c>
       <c r="B74" t="s" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C74" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D74" t="s" s="1">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="E74" t="s" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F74" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G74" t="n" s="1">
-        <v>1000.0</v>
+        <v>1201.89</v>
       </c>
       <c r="H74" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-1201.89</v>
       </c>
     </row>
     <row r="75">
@@ -2032,49 +2041,75 @@
         <v>26</v>
       </c>
       <c r="B75" t="s" s="1">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C75" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D75" t="s" s="1">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E75" t="s" s="1">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F75" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G75" t="n" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="H75" t="n" s="1">
+        <v>-1000.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B76" t="s" s="1">
+        <v>116</v>
+      </c>
+      <c r="C76" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D76" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="E76" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="F76" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G76" t="n" s="1">
         <v>3750.0</v>
       </c>
-      <c r="H75" t="n" s="1">
+      <c r="H76" t="n" s="1">
         <v>-3750.0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Dez_2026.xlsx
@@ -294,12 +294,6 @@
     <t>18/12/2026</t>
   </si>
   <si>
-    <t>104401 - 2</t>
-  </si>
-  <si>
-    <t>REGINA RURIKO TATEIGI</t>
-  </si>
-  <si>
     <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
   </si>
   <si>
@@ -351,6 +345,12 @@
     <t>25/12/2026</t>
   </si>
   <si>
+    <t>106001 - 2</t>
+  </si>
+  <si>
+    <t>Claudio Wasserman</t>
+  </si>
+  <si>
     <t>68 - 5</t>
   </si>
   <si>
@@ -375,7 +375,7 @@
     <t>Total Geral Crédito</t>
   </si>
   <si>
-    <t>11.342,40</t>
+    <t>7.784,12</t>
   </si>
   <si>
     <t>Total Geral Débito</t>
@@ -387,7 +387,7 @@
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-94.963,81</t>
+    <t>-98.522,09</t>
   </si>
 </sst>
 </file>
@@ -1706,22 +1706,22 @@
         <v>92</v>
       </c>
       <c r="C62" t="s" s="1">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="D62" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="E62" t="s" s="1">
         <v>93</v>
       </c>
-      <c r="E62" t="s" s="1">
-        <v>94</v>
-      </c>
       <c r="F62" t="n" s="1">
-        <v>7425.0</v>
+        <v>0.0</v>
       </c>
       <c r="G62" t="n" s="1">
-        <v>0.0</v>
+        <v>4588.5</v>
       </c>
       <c r="H62" t="n" s="1">
-        <v>7425.0</v>
+        <v>-4588.5</v>
       </c>
     </row>
     <row r="63">
@@ -1735,7 +1735,7 @@
         <v>28</v>
       </c>
       <c r="D63" t="s" s="1">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="E63" t="s" s="1">
         <v>95</v>
@@ -1744,10 +1744,10 @@
         <v>0.0</v>
       </c>
       <c r="G63" t="n" s="1">
-        <v>4588.5</v>
+        <v>239.58</v>
       </c>
       <c r="H63" t="n" s="1">
-        <v>-4588.5</v>
+        <v>-239.58</v>
       </c>
     </row>
     <row r="64">
@@ -1758,22 +1758,22 @@
         <v>92</v>
       </c>
       <c r="C64" t="s" s="1">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s" s="1">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="E64" t="s" s="1">
         <v>97</v>
       </c>
       <c r="F64" t="n" s="1">
-        <v>0.0</v>
+        <v>840.0</v>
       </c>
       <c r="G64" t="n" s="1">
-        <v>239.58</v>
+        <v>0.0</v>
       </c>
       <c r="H64" t="n" s="1">
-        <v>-239.58</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="65">
@@ -1781,25 +1781,25 @@
         <v>26</v>
       </c>
       <c r="B65" t="s" s="1">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C65" t="s" s="1">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="D65" t="s" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E65" t="s" s="1">
         <v>99</v>
       </c>
       <c r="F65" t="n" s="1">
-        <v>840.0</v>
+        <v>0.0</v>
       </c>
       <c r="G65" t="n" s="1">
-        <v>0.0</v>
+        <v>1500.0</v>
       </c>
       <c r="H65" t="n" s="1">
-        <v>840.0</v>
+        <v>-1500.0</v>
       </c>
     </row>
     <row r="66">
@@ -1807,7 +1807,7 @@
         <v>26</v>
       </c>
       <c r="B66" t="s" s="1">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C66" t="s" s="1">
         <v>28</v>
@@ -1816,16 +1816,16 @@
         <v>37</v>
       </c>
       <c r="E66" t="s" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F66" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G66" t="n" s="1">
-        <v>1500.0</v>
+        <v>4500.0</v>
       </c>
       <c r="H66" t="n" s="1">
-        <v>-1500.0</v>
+        <v>-4500.0</v>
       </c>
     </row>
     <row r="67">
@@ -1833,7 +1833,7 @@
         <v>26</v>
       </c>
       <c r="B67" t="s" s="1">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C67" t="s" s="1">
         <v>28</v>
@@ -1842,16 +1842,16 @@
         <v>37</v>
       </c>
       <c r="E67" t="s" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F67" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G67" t="n" s="1">
-        <v>4500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="H67" t="n" s="1">
-        <v>-4500.0</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="68">
@@ -1859,7 +1859,7 @@
         <v>26</v>
       </c>
       <c r="B68" t="s" s="1">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C68" t="s" s="1">
         <v>28</v>
@@ -1868,16 +1868,16 @@
         <v>37</v>
       </c>
       <c r="E68" t="s" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F68" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G68" t="n" s="1">
-        <v>15000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="H68" t="n" s="1">
-        <v>-15000.0</v>
+        <v>-2000.0</v>
       </c>
     </row>
     <row r="69">
@@ -1885,25 +1885,25 @@
         <v>26</v>
       </c>
       <c r="B69" t="s" s="1">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C69" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D69" t="s" s="1">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="E69" t="s" s="1">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F69" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G69" t="n" s="1">
-        <v>2000.0</v>
+        <v>146.67</v>
       </c>
       <c r="H69" t="n" s="1">
-        <v>-2000.0</v>
+        <v>-146.67</v>
       </c>
     </row>
     <row r="70">
@@ -1911,25 +1911,25 @@
         <v>26</v>
       </c>
       <c r="B70" t="s" s="1">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C70" t="s" s="1">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="D70" t="s" s="1">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E70" t="s" s="1">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F70" t="n" s="1">
-        <v>0.0</v>
+        <v>1260.87</v>
       </c>
       <c r="G70" t="n" s="1">
-        <v>146.67</v>
+        <v>0.0</v>
       </c>
       <c r="H70" t="n" s="1">
-        <v>-146.67</v>
+        <v>1260.87</v>
       </c>
     </row>
     <row r="71">
@@ -1937,25 +1937,25 @@
         <v>26</v>
       </c>
       <c r="B71" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C71" t="s" s="1">
         <v>89</v>
       </c>
       <c r="D71" t="s" s="1">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E71" t="s" s="1">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F71" t="n" s="1">
-        <v>1260.87</v>
+        <v>3866.72</v>
       </c>
       <c r="G71" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="H71" t="n" s="1">
-        <v>1260.87</v>
+        <v>3866.72</v>
       </c>
     </row>
     <row r="72">
@@ -1963,7 +1963,7 @@
         <v>26</v>
       </c>
       <c r="B72" t="s" s="1">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C72" t="s" s="1">
         <v>28</v>
@@ -1989,7 +1989,7 @@
         <v>26</v>
       </c>
       <c r="B73" t="s" s="1">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C73" t="s" s="1">
         <v>28</v>
